--- a/data/clean/producao_agricola.xlsx
+++ b/data/clean/producao_agricola.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I304"/>
+  <dimension ref="A1:I307"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6059,81 +6059,65 @@
     </row>
     <row r="153">
       <c r="A153" s="1" t="n">
-        <v>0</v>
+        <v>151</v>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Sao Paulo</t>
+          <t>Parana</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>janeiro 2020</t>
+          <t>abril 2026</t>
         </is>
       </c>
       <c r="D153" t="n">
-        <v>333882</v>
+        <v>5819800</v>
       </c>
       <c r="E153" t="n">
-        <v>333800</v>
+        <v>5819800</v>
       </c>
       <c r="F153" t="n">
-        <v>2107900</v>
+        <v>21935300</v>
       </c>
       <c r="G153" t="n">
-        <v>6315</v>
+        <v>3769</v>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>milho</t>
+          <t>soja</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>2020-01</t>
+          <t>2026-04</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="1" t="n">
-        <v>1</v>
+        <v>152</v>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Sao Paulo</t>
-        </is>
-      </c>
-      <c r="C154" t="inlineStr">
-        <is>
-          <t>fevereiro 2020</t>
-        </is>
-      </c>
-      <c r="D154" t="n">
-        <v>333882</v>
-      </c>
-      <c r="E154" t="n">
-        <v>333800</v>
-      </c>
-      <c r="F154" t="n">
-        <v>2107900</v>
-      </c>
-      <c r="G154" t="n">
-        <v>6315</v>
-      </c>
+          <t>Fonte: IBGE - Levantamento Sistematico da Produçao Agrícola</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr"/>
+      <c r="D154" t="inlineStr"/>
+      <c r="E154" t="inlineStr"/>
+      <c r="F154" t="inlineStr"/>
+      <c r="G154" t="inlineStr"/>
       <c r="H154" t="inlineStr">
         <is>
-          <t>milho</t>
-        </is>
-      </c>
-      <c r="I154" t="inlineStr">
-        <is>
-          <t>2020-02</t>
-        </is>
-      </c>
+          <t>soja</t>
+        </is>
+      </c>
+      <c r="I154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" s="1" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B155" t="inlineStr">
         <is>
@@ -6142,7 +6126,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>março 2020</t>
+          <t>janeiro 2020</t>
         </is>
       </c>
       <c r="D155" t="n">
@@ -6164,13 +6148,13 @@
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t>2020-03</t>
+          <t>2020-01</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="1" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B156" t="inlineStr">
         <is>
@@ -6179,7 +6163,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>abril 2020</t>
+          <t>fevereiro 2020</t>
         </is>
       </c>
       <c r="D156" t="n">
@@ -6201,13 +6185,13 @@
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t>2020-04</t>
+          <t>2020-02</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="1" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B157" t="inlineStr">
         <is>
@@ -6216,7 +6200,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>maio 2020</t>
+          <t>março 2020</t>
         </is>
       </c>
       <c r="D157" t="n">
@@ -6238,13 +6222,13 @@
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>2020-05</t>
+          <t>2020-03</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="1" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B158" t="inlineStr">
         <is>
@@ -6253,20 +6237,20 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>junho 2020</t>
+          <t>abril 2020</t>
         </is>
       </c>
       <c r="D158" t="n">
-        <v>324899</v>
+        <v>333882</v>
       </c>
       <c r="E158" t="n">
-        <v>324897</v>
+        <v>333800</v>
       </c>
       <c r="F158" t="n">
-        <v>2171708</v>
+        <v>2107900</v>
       </c>
       <c r="G158" t="n">
-        <v>6684</v>
+        <v>6315</v>
       </c>
       <c r="H158" t="inlineStr">
         <is>
@@ -6275,13 +6259,13 @@
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t>2020-06</t>
+          <t>2020-04</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="1" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B159" t="inlineStr">
         <is>
@@ -6290,20 +6274,20 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>julho 2020</t>
+          <t>maio 2020</t>
         </is>
       </c>
       <c r="D159" t="n">
-        <v>324899</v>
+        <v>333882</v>
       </c>
       <c r="E159" t="n">
-        <v>324897</v>
+        <v>333800</v>
       </c>
       <c r="F159" t="n">
-        <v>2171708</v>
+        <v>2107900</v>
       </c>
       <c r="G159" t="n">
-        <v>6684</v>
+        <v>6315</v>
       </c>
       <c r="H159" t="inlineStr">
         <is>
@@ -6312,13 +6296,13 @@
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t>2020-07</t>
+          <t>2020-05</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="1" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B160" t="inlineStr">
         <is>
@@ -6327,7 +6311,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>agosto 2020</t>
+          <t>junho 2020</t>
         </is>
       </c>
       <c r="D160" t="n">
@@ -6349,13 +6333,13 @@
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t>2020-08</t>
+          <t>2020-06</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="1" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B161" t="inlineStr">
         <is>
@@ -6364,20 +6348,20 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>setembro 2020</t>
+          <t>julho 2020</t>
         </is>
       </c>
       <c r="D161" t="n">
-        <v>322689</v>
+        <v>324899</v>
       </c>
       <c r="E161" t="n">
-        <v>322687</v>
+        <v>324897</v>
       </c>
       <c r="F161" t="n">
-        <v>2172123</v>
+        <v>2171708</v>
       </c>
       <c r="G161" t="n">
-        <v>6731</v>
+        <v>6684</v>
       </c>
       <c r="H161" t="inlineStr">
         <is>
@@ -6386,13 +6370,13 @@
       </c>
       <c r="I161" t="inlineStr">
         <is>
-          <t>2020-09</t>
+          <t>2020-07</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="1" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B162" t="inlineStr">
         <is>
@@ -6401,20 +6385,20 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>outubro 2020</t>
+          <t>agosto 2020</t>
         </is>
       </c>
       <c r="D162" t="n">
-        <v>322689</v>
+        <v>324899</v>
       </c>
       <c r="E162" t="n">
-        <v>322687</v>
+        <v>324897</v>
       </c>
       <c r="F162" t="n">
-        <v>2172123</v>
+        <v>2171708</v>
       </c>
       <c r="G162" t="n">
-        <v>6731</v>
+        <v>6684</v>
       </c>
       <c r="H162" t="inlineStr">
         <is>
@@ -6423,13 +6407,13 @@
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t>2020-10</t>
+          <t>2020-08</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="1" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B163" t="inlineStr">
         <is>
@@ -6438,7 +6422,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>novembro 2020</t>
+          <t>setembro 2020</t>
         </is>
       </c>
       <c r="D163" t="n">
@@ -6460,13 +6444,13 @@
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t>2020-11</t>
+          <t>2020-09</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="1" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B164" t="inlineStr">
         <is>
@@ -6475,7 +6459,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>dezembro 2020</t>
+          <t>outubro 2020</t>
         </is>
       </c>
       <c r="D164" t="n">
@@ -6497,13 +6481,13 @@
       </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t>2020-12</t>
+          <t>2020-10</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="1" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B165" t="inlineStr">
         <is>
@@ -6512,20 +6496,20 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>janeiro 2021</t>
+          <t>novembro 2020</t>
         </is>
       </c>
       <c r="D165" t="n">
-        <v>335102</v>
+        <v>322689</v>
       </c>
       <c r="E165" t="n">
-        <v>335100</v>
+        <v>322687</v>
       </c>
       <c r="F165" t="n">
-        <v>1899300</v>
+        <v>2172123</v>
       </c>
       <c r="G165" t="n">
-        <v>5668</v>
+        <v>6731</v>
       </c>
       <c r="H165" t="inlineStr">
         <is>
@@ -6534,13 +6518,13 @@
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t>2021-01</t>
+          <t>2020-11</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="1" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B166" t="inlineStr">
         <is>
@@ -6549,20 +6533,20 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>fevereiro 2021</t>
+          <t>dezembro 2020</t>
         </is>
       </c>
       <c r="D166" t="n">
-        <v>335102</v>
+        <v>322689</v>
       </c>
       <c r="E166" t="n">
-        <v>335100</v>
+        <v>322687</v>
       </c>
       <c r="F166" t="n">
-        <v>1899300</v>
+        <v>2172123</v>
       </c>
       <c r="G166" t="n">
-        <v>5668</v>
+        <v>6731</v>
       </c>
       <c r="H166" t="inlineStr">
         <is>
@@ -6571,13 +6555,13 @@
       </c>
       <c r="I166" t="inlineStr">
         <is>
-          <t>2021-02</t>
+          <t>2020-12</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="1" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B167" t="inlineStr">
         <is>
@@ -6586,7 +6570,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>março 2021</t>
+          <t>janeiro 2021</t>
         </is>
       </c>
       <c r="D167" t="n">
@@ -6608,13 +6592,13 @@
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t>2021-03</t>
+          <t>2021-01</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="1" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B168" t="inlineStr">
         <is>
@@ -6623,20 +6607,20 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>abril 2021</t>
+          <t>fevereiro 2021</t>
         </is>
       </c>
       <c r="D168" t="n">
-        <v>323011</v>
+        <v>335102</v>
       </c>
       <c r="E168" t="n">
-        <v>323011</v>
+        <v>335100</v>
       </c>
       <c r="F168" t="n">
-        <v>2154160</v>
+        <v>1899300</v>
       </c>
       <c r="G168" t="n">
-        <v>6669</v>
+        <v>5668</v>
       </c>
       <c r="H168" t="inlineStr">
         <is>
@@ -6645,13 +6629,13 @@
       </c>
       <c r="I168" t="inlineStr">
         <is>
-          <t>2021-04</t>
+          <t>2021-02</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="1" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B169" t="inlineStr">
         <is>
@@ -6660,20 +6644,20 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>maio 2021</t>
+          <t>março 2021</t>
         </is>
       </c>
       <c r="D169" t="n">
-        <v>323011</v>
+        <v>335102</v>
       </c>
       <c r="E169" t="n">
-        <v>323011</v>
+        <v>335100</v>
       </c>
       <c r="F169" t="n">
-        <v>2154160</v>
+        <v>1899300</v>
       </c>
       <c r="G169" t="n">
-        <v>6669</v>
+        <v>5668</v>
       </c>
       <c r="H169" t="inlineStr">
         <is>
@@ -6682,13 +6666,13 @@
       </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t>2021-05</t>
+          <t>2021-03</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="1" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B170" t="inlineStr">
         <is>
@@ -6697,7 +6681,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>junho 2021</t>
+          <t>abril 2021</t>
         </is>
       </c>
       <c r="D170" t="n">
@@ -6719,13 +6703,13 @@
       </c>
       <c r="I170" t="inlineStr">
         <is>
-          <t>2021-06</t>
+          <t>2021-04</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="1" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B171" t="inlineStr">
         <is>
@@ -6734,7 +6718,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>julho 2021</t>
+          <t>maio 2021</t>
         </is>
       </c>
       <c r="D171" t="n">
@@ -6756,13 +6740,13 @@
       </c>
       <c r="I171" t="inlineStr">
         <is>
-          <t>2021-07</t>
+          <t>2021-05</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="1" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B172" t="inlineStr">
         <is>
@@ -6771,7 +6755,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>agosto 2021</t>
+          <t>junho 2021</t>
         </is>
       </c>
       <c r="D172" t="n">
@@ -6793,13 +6777,13 @@
       </c>
       <c r="I172" t="inlineStr">
         <is>
-          <t>2021-08</t>
+          <t>2021-06</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="1" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B173" t="inlineStr">
         <is>
@@ -6808,20 +6792,20 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>setembro 2021</t>
+          <t>julho 2021</t>
         </is>
       </c>
       <c r="D173" t="n">
-        <v>327662</v>
+        <v>323011</v>
       </c>
       <c r="E173" t="n">
-        <v>327662</v>
+        <v>323011</v>
       </c>
       <c r="F173" t="n">
-        <v>2281515</v>
+        <v>2154160</v>
       </c>
       <c r="G173" t="n">
-        <v>6963</v>
+        <v>6669</v>
       </c>
       <c r="H173" t="inlineStr">
         <is>
@@ -6830,13 +6814,13 @@
       </c>
       <c r="I173" t="inlineStr">
         <is>
-          <t>2021-09</t>
+          <t>2021-07</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="1" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B174" t="inlineStr">
         <is>
@@ -6845,20 +6829,20 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>outubro 2021</t>
+          <t>agosto 2021</t>
         </is>
       </c>
       <c r="D174" t="n">
-        <v>327662</v>
+        <v>323011</v>
       </c>
       <c r="E174" t="n">
-        <v>327662</v>
+        <v>323011</v>
       </c>
       <c r="F174" t="n">
-        <v>2281515</v>
+        <v>2154160</v>
       </c>
       <c r="G174" t="n">
-        <v>6963</v>
+        <v>6669</v>
       </c>
       <c r="H174" t="inlineStr">
         <is>
@@ -6867,13 +6851,13 @@
       </c>
       <c r="I174" t="inlineStr">
         <is>
-          <t>2021-10</t>
+          <t>2021-08</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="1" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B175" t="inlineStr">
         <is>
@@ -6882,7 +6866,7 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>novembro 2021</t>
+          <t>setembro 2021</t>
         </is>
       </c>
       <c r="D175" t="n">
@@ -6904,13 +6888,13 @@
       </c>
       <c r="I175" t="inlineStr">
         <is>
-          <t>2021-11</t>
+          <t>2021-09</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" s="1" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B176" t="inlineStr">
         <is>
@@ -6919,7 +6903,7 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>dezembro 2021</t>
+          <t>outubro 2021</t>
         </is>
       </c>
       <c r="D176" t="n">
@@ -6941,13 +6925,13 @@
       </c>
       <c r="I176" t="inlineStr">
         <is>
-          <t>2021-12</t>
+          <t>2021-10</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="1" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B177" t="inlineStr">
         <is>
@@ -6956,20 +6940,20 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>janeiro 2022</t>
+          <t>novembro 2021</t>
         </is>
       </c>
       <c r="D177" t="n">
-        <v>335100</v>
+        <v>327662</v>
       </c>
       <c r="E177" t="n">
-        <v>335100</v>
+        <v>327662</v>
       </c>
       <c r="F177" t="n">
-        <v>1845700</v>
+        <v>2281515</v>
       </c>
       <c r="G177" t="n">
-        <v>5508</v>
+        <v>6963</v>
       </c>
       <c r="H177" t="inlineStr">
         <is>
@@ -6978,13 +6962,13 @@
       </c>
       <c r="I177" t="inlineStr">
         <is>
-          <t>2022-01</t>
+          <t>2021-11</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="1" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B178" t="inlineStr">
         <is>
@@ -6993,20 +6977,20 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>fevereiro 2022</t>
+          <t>dezembro 2021</t>
         </is>
       </c>
       <c r="D178" t="n">
-        <v>335100</v>
+        <v>327662</v>
       </c>
       <c r="E178" t="n">
-        <v>335100</v>
+        <v>327662</v>
       </c>
       <c r="F178" t="n">
-        <v>1845700</v>
+        <v>2281515</v>
       </c>
       <c r="G178" t="n">
-        <v>5508</v>
+        <v>6963</v>
       </c>
       <c r="H178" t="inlineStr">
         <is>
@@ -7015,13 +6999,13 @@
       </c>
       <c r="I178" t="inlineStr">
         <is>
-          <t>2022-02</t>
+          <t>2021-12</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" s="1" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B179" t="inlineStr">
         <is>
@@ -7030,7 +7014,7 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>março 2022</t>
+          <t>janeiro 2022</t>
         </is>
       </c>
       <c r="D179" t="n">
@@ -7052,13 +7036,13 @@
       </c>
       <c r="I179" t="inlineStr">
         <is>
-          <t>2022-03</t>
+          <t>2022-01</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="1" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B180" t="inlineStr">
         <is>
@@ -7067,20 +7051,20 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>abril 2022</t>
+          <t>fevereiro 2022</t>
         </is>
       </c>
       <c r="D180" t="n">
-        <v>332496</v>
+        <v>335100</v>
       </c>
       <c r="E180" t="n">
-        <v>332496</v>
+        <v>335100</v>
       </c>
       <c r="F180" t="n">
-        <v>2211803</v>
+        <v>1845700</v>
       </c>
       <c r="G180" t="n">
-        <v>6652</v>
+        <v>5508</v>
       </c>
       <c r="H180" t="inlineStr">
         <is>
@@ -7089,13 +7073,13 @@
       </c>
       <c r="I180" t="inlineStr">
         <is>
-          <t>2022-04</t>
+          <t>2022-02</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" s="1" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B181" t="inlineStr">
         <is>
@@ -7104,20 +7088,20 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>maio 2022</t>
+          <t>março 2022</t>
         </is>
       </c>
       <c r="D181" t="n">
-        <v>332496</v>
+        <v>335100</v>
       </c>
       <c r="E181" t="n">
-        <v>332496</v>
+        <v>335100</v>
       </c>
       <c r="F181" t="n">
-        <v>2211803</v>
+        <v>1845700</v>
       </c>
       <c r="G181" t="n">
-        <v>6652</v>
+        <v>5508</v>
       </c>
       <c r="H181" t="inlineStr">
         <is>
@@ -7126,13 +7110,13 @@
       </c>
       <c r="I181" t="inlineStr">
         <is>
-          <t>2022-05</t>
+          <t>2022-03</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" s="1" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B182" t="inlineStr">
         <is>
@@ -7141,7 +7125,7 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>junho 2022</t>
+          <t>abril 2022</t>
         </is>
       </c>
       <c r="D182" t="n">
@@ -7163,13 +7147,13 @@
       </c>
       <c r="I182" t="inlineStr">
         <is>
-          <t>2022-06</t>
+          <t>2022-04</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" s="1" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B183" t="inlineStr">
         <is>
@@ -7178,7 +7162,7 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>julho 2022</t>
+          <t>maio 2022</t>
         </is>
       </c>
       <c r="D183" t="n">
@@ -7200,13 +7184,13 @@
       </c>
       <c r="I183" t="inlineStr">
         <is>
-          <t>2022-07</t>
+          <t>2022-05</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" s="1" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B184" t="inlineStr">
         <is>
@@ -7215,7 +7199,7 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>agosto 2022</t>
+          <t>junho 2022</t>
         </is>
       </c>
       <c r="D184" t="n">
@@ -7237,13 +7221,13 @@
       </c>
       <c r="I184" t="inlineStr">
         <is>
-          <t>2022-08</t>
+          <t>2022-06</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" s="1" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B185" t="inlineStr">
         <is>
@@ -7252,20 +7236,20 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>setembro 2022</t>
+          <t>julho 2022</t>
         </is>
       </c>
       <c r="D185" t="n">
-        <v>335100</v>
+        <v>332496</v>
       </c>
       <c r="E185" t="n">
-        <v>335100</v>
+        <v>332496</v>
       </c>
       <c r="F185" t="n">
-        <v>1995500</v>
+        <v>2211803</v>
       </c>
       <c r="G185" t="n">
-        <v>5955</v>
+        <v>6652</v>
       </c>
       <c r="H185" t="inlineStr">
         <is>
@@ -7274,13 +7258,13 @@
       </c>
       <c r="I185" t="inlineStr">
         <is>
-          <t>2022-09</t>
+          <t>2022-07</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" s="1" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B186" t="inlineStr">
         <is>
@@ -7289,20 +7273,20 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>outubro 2022</t>
+          <t>agosto 2022</t>
         </is>
       </c>
       <c r="D186" t="n">
-        <v>335100</v>
+        <v>332496</v>
       </c>
       <c r="E186" t="n">
-        <v>335100</v>
+        <v>332496</v>
       </c>
       <c r="F186" t="n">
-        <v>1995500</v>
+        <v>2211803</v>
       </c>
       <c r="G186" t="n">
-        <v>5955</v>
+        <v>6652</v>
       </c>
       <c r="H186" t="inlineStr">
         <is>
@@ -7311,13 +7295,13 @@
       </c>
       <c r="I186" t="inlineStr">
         <is>
-          <t>2022-10</t>
+          <t>2022-08</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" s="1" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B187" t="inlineStr">
         <is>
@@ -7326,7 +7310,7 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>novembro 2022</t>
+          <t>setembro 2022</t>
         </is>
       </c>
       <c r="D187" t="n">
@@ -7348,13 +7332,13 @@
       </c>
       <c r="I187" t="inlineStr">
         <is>
-          <t>2022-11</t>
+          <t>2022-09</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" s="1" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B188" t="inlineStr">
         <is>
@@ -7363,7 +7347,7 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>dezembro 2022</t>
+          <t>outubro 2022</t>
         </is>
       </c>
       <c r="D188" t="n">
@@ -7385,13 +7369,13 @@
       </c>
       <c r="I188" t="inlineStr">
         <is>
-          <t>2022-12</t>
+          <t>2022-10</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" s="1" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B189" t="inlineStr">
         <is>
@@ -7400,20 +7384,20 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>janeiro 2023</t>
+          <t>novembro 2022</t>
         </is>
       </c>
       <c r="D189" t="n">
-        <v>341263</v>
+        <v>335100</v>
       </c>
       <c r="E189" t="n">
-        <v>341263</v>
+        <v>335100</v>
       </c>
       <c r="F189" t="n">
-        <v>2263352</v>
+        <v>1995500</v>
       </c>
       <c r="G189" t="n">
-        <v>6632</v>
+        <v>5955</v>
       </c>
       <c r="H189" t="inlineStr">
         <is>
@@ -7422,13 +7406,13 @@
       </c>
       <c r="I189" t="inlineStr">
         <is>
-          <t>2023-01</t>
+          <t>2022-11</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" s="1" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B190" t="inlineStr">
         <is>
@@ -7437,20 +7421,20 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>fevereiro 2023</t>
+          <t>dezembro 2022</t>
         </is>
       </c>
       <c r="D190" t="n">
-        <v>341263</v>
+        <v>335100</v>
       </c>
       <c r="E190" t="n">
-        <v>341263</v>
+        <v>335100</v>
       </c>
       <c r="F190" t="n">
-        <v>2263352</v>
+        <v>1995500</v>
       </c>
       <c r="G190" t="n">
-        <v>6632</v>
+        <v>5955</v>
       </c>
       <c r="H190" t="inlineStr">
         <is>
@@ -7459,13 +7443,13 @@
       </c>
       <c r="I190" t="inlineStr">
         <is>
-          <t>2023-02</t>
+          <t>2022-12</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" s="1" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B191" t="inlineStr">
         <is>
@@ -7474,7 +7458,7 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>março 2023</t>
+          <t>janeiro 2023</t>
         </is>
       </c>
       <c r="D191" t="n">
@@ -7496,13 +7480,13 @@
       </c>
       <c r="I191" t="inlineStr">
         <is>
-          <t>2023-03</t>
+          <t>2023-01</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" s="1" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B192" t="inlineStr">
         <is>
@@ -7511,20 +7495,20 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>abril 2023</t>
+          <t>fevereiro 2023</t>
         </is>
       </c>
       <c r="D192" t="n">
-        <v>310840</v>
+        <v>341263</v>
       </c>
       <c r="E192" t="n">
-        <v>310800</v>
+        <v>341263</v>
       </c>
       <c r="F192" t="n">
-        <v>2132400</v>
+        <v>2263352</v>
       </c>
       <c r="G192" t="n">
-        <v>6861</v>
+        <v>6632</v>
       </c>
       <c r="H192" t="inlineStr">
         <is>
@@ -7533,13 +7517,13 @@
       </c>
       <c r="I192" t="inlineStr">
         <is>
-          <t>2023-04</t>
+          <t>2023-02</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" s="1" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B193" t="inlineStr">
         <is>
@@ -7548,20 +7532,20 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>maio 2023</t>
+          <t>março 2023</t>
         </is>
       </c>
       <c r="D193" t="n">
-        <v>310840</v>
+        <v>341263</v>
       </c>
       <c r="E193" t="n">
-        <v>310800</v>
+        <v>341263</v>
       </c>
       <c r="F193" t="n">
-        <v>2132400</v>
+        <v>2263352</v>
       </c>
       <c r="G193" t="n">
-        <v>6861</v>
+        <v>6632</v>
       </c>
       <c r="H193" t="inlineStr">
         <is>
@@ -7570,13 +7554,13 @@
       </c>
       <c r="I193" t="inlineStr">
         <is>
-          <t>2023-05</t>
+          <t>2023-03</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" s="1" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B194" t="inlineStr">
         <is>
@@ -7585,7 +7569,7 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>junho 2023</t>
+          <t>abril 2023</t>
         </is>
       </c>
       <c r="D194" t="n">
@@ -7607,13 +7591,13 @@
       </c>
       <c r="I194" t="inlineStr">
         <is>
-          <t>2023-06</t>
+          <t>2023-04</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" s="1" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B195" t="inlineStr">
         <is>
@@ -7622,7 +7606,7 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>julho 2023</t>
+          <t>maio 2023</t>
         </is>
       </c>
       <c r="D195" t="n">
@@ -7644,13 +7628,13 @@
       </c>
       <c r="I195" t="inlineStr">
         <is>
-          <t>2023-07</t>
+          <t>2023-05</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" s="1" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B196" t="inlineStr">
         <is>
@@ -7659,7 +7643,7 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>agosto 2023</t>
+          <t>junho 2023</t>
         </is>
       </c>
       <c r="D196" t="n">
@@ -7681,13 +7665,13 @@
       </c>
       <c r="I196" t="inlineStr">
         <is>
-          <t>2023-08</t>
+          <t>2023-06</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" s="1" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B197" t="inlineStr">
         <is>
@@ -7696,20 +7680,20 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>setembro 2023</t>
+          <t>julho 2023</t>
         </is>
       </c>
       <c r="D197" t="n">
-        <v>305486</v>
+        <v>310840</v>
       </c>
       <c r="E197" t="n">
-        <v>305456</v>
+        <v>310800</v>
       </c>
       <c r="F197" t="n">
-        <v>2029358</v>
+        <v>2132400</v>
       </c>
       <c r="G197" t="n">
-        <v>6644</v>
+        <v>6861</v>
       </c>
       <c r="H197" t="inlineStr">
         <is>
@@ -7718,13 +7702,13 @@
       </c>
       <c r="I197" t="inlineStr">
         <is>
-          <t>2023-09</t>
+          <t>2023-07</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" s="1" t="n">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B198" t="inlineStr">
         <is>
@@ -7733,20 +7717,20 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>outubro 2023</t>
+          <t>agosto 2023</t>
         </is>
       </c>
       <c r="D198" t="n">
-        <v>305486</v>
+        <v>310840</v>
       </c>
       <c r="E198" t="n">
-        <v>305456</v>
+        <v>310800</v>
       </c>
       <c r="F198" t="n">
-        <v>2029358</v>
+        <v>2132400</v>
       </c>
       <c r="G198" t="n">
-        <v>6644</v>
+        <v>6861</v>
       </c>
       <c r="H198" t="inlineStr">
         <is>
@@ -7755,13 +7739,13 @@
       </c>
       <c r="I198" t="inlineStr">
         <is>
-          <t>2023-10</t>
+          <t>2023-08</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" s="1" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B199" t="inlineStr">
         <is>
@@ -7770,7 +7754,7 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>novembro 2023</t>
+          <t>setembro 2023</t>
         </is>
       </c>
       <c r="D199" t="n">
@@ -7792,13 +7776,13 @@
       </c>
       <c r="I199" t="inlineStr">
         <is>
-          <t>2023-11</t>
+          <t>2023-09</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" s="1" t="n">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B200" t="inlineStr">
         <is>
@@ -7807,7 +7791,7 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>dezembro 2023</t>
+          <t>outubro 2023</t>
         </is>
       </c>
       <c r="D200" t="n">
@@ -7829,13 +7813,13 @@
       </c>
       <c r="I200" t="inlineStr">
         <is>
-          <t>2023-12</t>
+          <t>2023-10</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" s="1" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B201" t="inlineStr">
         <is>
@@ -7844,20 +7828,20 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>janeiro 2024</t>
+          <t>novembro 2023</t>
         </is>
       </c>
       <c r="D201" t="n">
-        <v>286630</v>
+        <v>305486</v>
       </c>
       <c r="E201" t="n">
-        <v>286600</v>
+        <v>305456</v>
       </c>
       <c r="F201" t="n">
-        <v>1819900</v>
+        <v>2029358</v>
       </c>
       <c r="G201" t="n">
-        <v>6350</v>
+        <v>6644</v>
       </c>
       <c r="H201" t="inlineStr">
         <is>
@@ -7866,13 +7850,13 @@
       </c>
       <c r="I201" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2023-11</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" s="1" t="n">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B202" t="inlineStr">
         <is>
@@ -7881,20 +7865,20 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>fevereiro 2024</t>
+          <t>dezembro 2023</t>
         </is>
       </c>
       <c r="D202" t="n">
-        <v>286630</v>
+        <v>305486</v>
       </c>
       <c r="E202" t="n">
-        <v>286600</v>
+        <v>305456</v>
       </c>
       <c r="F202" t="n">
-        <v>1819900</v>
+        <v>2029358</v>
       </c>
       <c r="G202" t="n">
-        <v>6350</v>
+        <v>6644</v>
       </c>
       <c r="H202" t="inlineStr">
         <is>
@@ -7903,13 +7887,13 @@
       </c>
       <c r="I202" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2023-12</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" s="1" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B203" t="inlineStr">
         <is>
@@ -7918,7 +7902,7 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>março 2024</t>
+          <t>janeiro 2024</t>
         </is>
       </c>
       <c r="D203" t="n">
@@ -7940,13 +7924,13 @@
       </c>
       <c r="I203" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-01</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" s="1" t="n">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B204" t="inlineStr">
         <is>
@@ -7955,20 +7939,20 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>abril 2024</t>
+          <t>fevereiro 2024</t>
         </is>
       </c>
       <c r="D204" t="n">
-        <v>286460</v>
+        <v>286630</v>
       </c>
       <c r="E204" t="n">
-        <v>286000</v>
+        <v>286600</v>
       </c>
       <c r="F204" t="n">
-        <v>1624500</v>
+        <v>1819900</v>
       </c>
       <c r="G204" t="n">
-        <v>5680</v>
+        <v>6350</v>
       </c>
       <c r="H204" t="inlineStr">
         <is>
@@ -7977,13 +7961,13 @@
       </c>
       <c r="I204" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-02</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" s="1" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B205" t="inlineStr">
         <is>
@@ -7992,20 +7976,20 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>maio 2024</t>
+          <t>março 2024</t>
         </is>
       </c>
       <c r="D205" t="n">
-        <v>286460</v>
+        <v>286630</v>
       </c>
       <c r="E205" t="n">
-        <v>286000</v>
+        <v>286600</v>
       </c>
       <c r="F205" t="n">
-        <v>1624500</v>
+        <v>1819900</v>
       </c>
       <c r="G205" t="n">
-        <v>5680</v>
+        <v>6350</v>
       </c>
       <c r="H205" t="inlineStr">
         <is>
@@ -8014,13 +7998,13 @@
       </c>
       <c r="I205" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-03</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" s="1" t="n">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B206" t="inlineStr">
         <is>
@@ -8029,7 +8013,7 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>junho 2024</t>
+          <t>abril 2024</t>
         </is>
       </c>
       <c r="D206" t="n">
@@ -8051,13 +8035,13 @@
       </c>
       <c r="I206" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2024-04</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" s="1" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B207" t="inlineStr">
         <is>
@@ -8066,7 +8050,7 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>julho 2024</t>
+          <t>maio 2024</t>
         </is>
       </c>
       <c r="D207" t="n">
@@ -8088,13 +8072,13 @@
       </c>
       <c r="I207" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2024-05</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" s="1" t="n">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B208" t="inlineStr">
         <is>
@@ -8103,7 +8087,7 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>agosto 2024</t>
+          <t>junho 2024</t>
         </is>
       </c>
       <c r="D208" t="n">
@@ -8125,13 +8109,13 @@
       </c>
       <c r="I208" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2024-06</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" s="1" t="n">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B209" t="inlineStr">
         <is>
@@ -8140,20 +8124,20 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>setembro 2024</t>
+          <t>julho 2024</t>
         </is>
       </c>
       <c r="D209" t="n">
-        <v>287422</v>
+        <v>286460</v>
       </c>
       <c r="E209" t="n">
         <v>286000</v>
       </c>
       <c r="F209" t="n">
-        <v>1573000</v>
+        <v>1624500</v>
       </c>
       <c r="G209" t="n">
-        <v>5500</v>
+        <v>5680</v>
       </c>
       <c r="H209" t="inlineStr">
         <is>
@@ -8162,13 +8146,13 @@
       </c>
       <c r="I209" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2024-07</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" s="1" t="n">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B210" t="inlineStr">
         <is>
@@ -8177,20 +8161,20 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>outubro 2024</t>
+          <t>agosto 2024</t>
         </is>
       </c>
       <c r="D210" t="n">
-        <v>287422</v>
+        <v>286460</v>
       </c>
       <c r="E210" t="n">
         <v>286000</v>
       </c>
       <c r="F210" t="n">
-        <v>1573000</v>
+        <v>1624500</v>
       </c>
       <c r="G210" t="n">
-        <v>5500</v>
+        <v>5680</v>
       </c>
       <c r="H210" t="inlineStr">
         <is>
@@ -8199,13 +8183,13 @@
       </c>
       <c r="I210" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2024-08</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" s="1" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B211" t="inlineStr">
         <is>
@@ -8214,7 +8198,7 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>novembro 2024</t>
+          <t>setembro 2024</t>
         </is>
       </c>
       <c r="D211" t="n">
@@ -8236,13 +8220,13 @@
       </c>
       <c r="I211" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2024-09</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" s="1" t="n">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B212" t="inlineStr">
         <is>
@@ -8251,11 +8235,11 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>dezembro 2024</t>
+          <t>outubro 2024</t>
         </is>
       </c>
       <c r="D212" t="n">
-        <v>287939</v>
+        <v>287422</v>
       </c>
       <c r="E212" t="n">
         <v>286000</v>
@@ -8273,13 +8257,13 @@
       </c>
       <c r="I212" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2024-10</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" s="1" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="B213" t="inlineStr">
         <is>
@@ -8288,20 +8272,20 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>janeiro 2025</t>
+          <t>novembro 2024</t>
         </is>
       </c>
       <c r="D213" t="n">
-        <v>267122</v>
+        <v>287422</v>
       </c>
       <c r="E213" t="n">
-        <v>265700</v>
+        <v>286000</v>
       </c>
       <c r="F213" t="n">
-        <v>1575100</v>
+        <v>1573000</v>
       </c>
       <c r="G213" t="n">
-        <v>5928</v>
+        <v>5500</v>
       </c>
       <c r="H213" t="inlineStr">
         <is>
@@ -8310,13 +8294,13 @@
       </c>
       <c r="I213" t="inlineStr">
         <is>
-          <t>2025-01</t>
+          <t>2024-11</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" s="1" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B214" t="inlineStr">
         <is>
@@ -8325,20 +8309,20 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>fevereiro 2025</t>
+          <t>dezembro 2024</t>
         </is>
       </c>
       <c r="D214" t="n">
-        <v>267122</v>
+        <v>287939</v>
       </c>
       <c r="E214" t="n">
-        <v>265700</v>
+        <v>286000</v>
       </c>
       <c r="F214" t="n">
-        <v>1575100</v>
+        <v>1573000</v>
       </c>
       <c r="G214" t="n">
-        <v>5928</v>
+        <v>5500</v>
       </c>
       <c r="H214" t="inlineStr">
         <is>
@@ -8347,13 +8331,13 @@
       </c>
       <c r="I214" t="inlineStr">
         <is>
-          <t>2025-02</t>
+          <t>2024-12</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" s="1" t="n">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B215" t="inlineStr">
         <is>
@@ -8362,11 +8346,11 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>março 2025</t>
+          <t>janeiro 2025</t>
         </is>
       </c>
       <c r="D215" t="n">
-        <v>266400</v>
+        <v>267122</v>
       </c>
       <c r="E215" t="n">
         <v>265700</v>
@@ -8384,13 +8368,13 @@
       </c>
       <c r="I215" t="inlineStr">
         <is>
-          <t>2025-03</t>
+          <t>2025-01</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" s="1" t="n">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B216" t="inlineStr">
         <is>
@@ -8399,11 +8383,11 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>abril 2025</t>
+          <t>fevereiro 2025</t>
         </is>
       </c>
       <c r="D216" t="n">
-        <v>266400</v>
+        <v>267122</v>
       </c>
       <c r="E216" t="n">
         <v>265700</v>
@@ -8421,13 +8405,13 @@
       </c>
       <c r="I216" t="inlineStr">
         <is>
-          <t>2025-04</t>
+          <t>2025-02</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" s="1" t="n">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="B217" t="inlineStr">
         <is>
@@ -8436,7 +8420,7 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>maio 2025</t>
+          <t>março 2025</t>
         </is>
       </c>
       <c r="D217" t="n">
@@ -8458,13 +8442,13 @@
       </c>
       <c r="I217" t="inlineStr">
         <is>
-          <t>2025-05</t>
+          <t>2025-03</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" s="1" t="n">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="B218" t="inlineStr">
         <is>
@@ -8473,7 +8457,7 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>junho 2025</t>
+          <t>abril 2025</t>
         </is>
       </c>
       <c r="D218" t="n">
@@ -8495,13 +8479,13 @@
       </c>
       <c r="I218" t="inlineStr">
         <is>
-          <t>2025-06</t>
+          <t>2025-04</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" s="1" t="n">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B219" t="inlineStr">
         <is>
@@ -8510,7 +8494,7 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>julho 2025</t>
+          <t>maio 2025</t>
         </is>
       </c>
       <c r="D219" t="n">
@@ -8532,13 +8516,13 @@
       </c>
       <c r="I219" t="inlineStr">
         <is>
-          <t>2025-07</t>
+          <t>2025-05</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" s="1" t="n">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B220" t="inlineStr">
         <is>
@@ -8547,7 +8531,7 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>agosto 2025</t>
+          <t>junho 2025</t>
         </is>
       </c>
       <c r="D220" t="n">
@@ -8569,13 +8553,13 @@
       </c>
       <c r="I220" t="inlineStr">
         <is>
-          <t>2025-08</t>
+          <t>2025-06</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" s="1" t="n">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="B221" t="inlineStr">
         <is>
@@ -8584,7 +8568,7 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>setembro 2025</t>
+          <t>julho 2025</t>
         </is>
       </c>
       <c r="D221" t="n">
@@ -8606,13 +8590,13 @@
       </c>
       <c r="I221" t="inlineStr">
         <is>
-          <t>2025-09</t>
+          <t>2025-07</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" s="1" t="n">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B222" t="inlineStr">
         <is>
@@ -8621,20 +8605,20 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>outubro 2025</t>
+          <t>agosto 2025</t>
         </is>
       </c>
       <c r="D222" t="n">
-        <v>265815</v>
+        <v>266400</v>
       </c>
       <c r="E222" t="n">
         <v>265700</v>
       </c>
       <c r="F222" t="n">
-        <v>1596900</v>
+        <v>1575100</v>
       </c>
       <c r="G222" t="n">
-        <v>6010</v>
+        <v>5928</v>
       </c>
       <c r="H222" t="inlineStr">
         <is>
@@ -8643,13 +8627,13 @@
       </c>
       <c r="I222" t="inlineStr">
         <is>
-          <t>2025-10</t>
+          <t>2025-08</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" s="1" t="n">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B223" t="inlineStr">
         <is>
@@ -8658,20 +8642,20 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>novembro 2025</t>
+          <t>setembro 2025</t>
         </is>
       </c>
       <c r="D223" t="n">
-        <v>265815</v>
+        <v>266400</v>
       </c>
       <c r="E223" t="n">
         <v>265700</v>
       </c>
       <c r="F223" t="n">
-        <v>1596900</v>
+        <v>1575100</v>
       </c>
       <c r="G223" t="n">
-        <v>6010</v>
+        <v>5928</v>
       </c>
       <c r="H223" t="inlineStr">
         <is>
@@ -8680,13 +8664,13 @@
       </c>
       <c r="I223" t="inlineStr">
         <is>
-          <t>2025-11</t>
+          <t>2025-09</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" s="1" t="n">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="B224" t="inlineStr">
         <is>
@@ -8695,7 +8679,7 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>dezembro 2025</t>
+          <t>outubro 2025</t>
         </is>
       </c>
       <c r="D224" t="n">
@@ -8717,13 +8701,13 @@
       </c>
       <c r="I224" t="inlineStr">
         <is>
-          <t>2025-12</t>
+          <t>2025-10</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" s="1" t="n">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B225" t="inlineStr">
         <is>
@@ -8732,20 +8716,20 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>janeiro 2026</t>
+          <t>novembro 2025</t>
         </is>
       </c>
       <c r="D225" t="n">
-        <v>279721</v>
+        <v>265815</v>
       </c>
       <c r="E225" t="n">
-        <v>278700</v>
+        <v>265700</v>
       </c>
       <c r="F225" t="n">
-        <v>1809000</v>
+        <v>1596900</v>
       </c>
       <c r="G225" t="n">
-        <v>6491</v>
+        <v>6010</v>
       </c>
       <c r="H225" t="inlineStr">
         <is>
@@ -8754,13 +8738,13 @@
       </c>
       <c r="I225" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2025-11</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" s="1" t="n">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B226" t="inlineStr">
         <is>
@@ -8769,20 +8753,20 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>fevereiro 2026</t>
+          <t>dezembro 2025</t>
         </is>
       </c>
       <c r="D226" t="n">
-        <v>279721</v>
+        <v>265815</v>
       </c>
       <c r="E226" t="n">
-        <v>278700</v>
+        <v>265700</v>
       </c>
       <c r="F226" t="n">
-        <v>1809000</v>
+        <v>1596900</v>
       </c>
       <c r="G226" t="n">
-        <v>6491</v>
+        <v>6010</v>
       </c>
       <c r="H226" t="inlineStr">
         <is>
@@ -8791,13 +8775,13 @@
       </c>
       <c r="I226" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2025-12</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" s="1" t="n">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B227" t="inlineStr">
         <is>
@@ -8806,7 +8790,7 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>março 2026</t>
+          <t>janeiro 2026</t>
         </is>
       </c>
       <c r="D227" t="n">
@@ -8828,13 +8812,13 @@
       </c>
       <c r="I227" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-01</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" s="1" t="n">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B228" t="inlineStr">
         <is>
@@ -8843,20 +8827,20 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>abril 2026</t>
+          <t>fevereiro 2026</t>
         </is>
       </c>
       <c r="D228" t="n">
-        <v>267503</v>
+        <v>279721</v>
       </c>
       <c r="E228" t="n">
-        <v>266482</v>
+        <v>278700</v>
       </c>
       <c r="F228" t="n">
-        <v>1857627</v>
+        <v>1809000</v>
       </c>
       <c r="G228" t="n">
-        <v>6971</v>
+        <v>6491</v>
       </c>
       <c r="H228" t="inlineStr">
         <is>
@@ -8865,35 +8849,35 @@
       </c>
       <c r="I228" t="inlineStr">
         <is>
-          <t>2026-04</t>
+          <t>2026-02</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" s="1" t="n">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>Parana</t>
+          <t>Sao Paulo</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>janeiro 2020</t>
+          <t>março 2026</t>
         </is>
       </c>
       <c r="D229" t="n">
-        <v>348801</v>
+        <v>279721</v>
       </c>
       <c r="E229" t="n">
-        <v>348801</v>
+        <v>278700</v>
       </c>
       <c r="F229" t="n">
-        <v>3246989</v>
+        <v>1809000</v>
       </c>
       <c r="G229" t="n">
-        <v>9309</v>
+        <v>6491</v>
       </c>
       <c r="H229" t="inlineStr">
         <is>
@@ -8902,35 +8886,35 @@
       </c>
       <c r="I229" t="inlineStr">
         <is>
-          <t>2020-01</t>
+          <t>2026-03</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" s="1" t="n">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>Parana</t>
+          <t>Sao Paulo</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>fevereiro 2020</t>
+          <t>abril 2026</t>
         </is>
       </c>
       <c r="D230" t="n">
-        <v>348801</v>
+        <v>267503</v>
       </c>
       <c r="E230" t="n">
-        <v>348801</v>
+        <v>266482</v>
       </c>
       <c r="F230" t="n">
-        <v>3308937</v>
+        <v>1857627</v>
       </c>
       <c r="G230" t="n">
-        <v>9487</v>
+        <v>6971</v>
       </c>
       <c r="H230" t="inlineStr">
         <is>
@@ -8939,13 +8923,13 @@
       </c>
       <c r="I230" t="inlineStr">
         <is>
-          <t>2020-02</t>
+          <t>2026-04</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" s="1" t="n">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B231" t="inlineStr">
         <is>
@@ -8954,20 +8938,20 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>março 2020</t>
+          <t>janeiro 2020</t>
         </is>
       </c>
       <c r="D231" t="n">
-        <v>351971</v>
+        <v>348801</v>
       </c>
       <c r="E231" t="n">
-        <v>351971</v>
+        <v>348801</v>
       </c>
       <c r="F231" t="n">
-        <v>3453339</v>
+        <v>3246989</v>
       </c>
       <c r="G231" t="n">
-        <v>9811</v>
+        <v>9309</v>
       </c>
       <c r="H231" t="inlineStr">
         <is>
@@ -8976,13 +8960,13 @@
       </c>
       <c r="I231" t="inlineStr">
         <is>
-          <t>2020-03</t>
+          <t>2020-01</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" s="1" t="n">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="B232" t="inlineStr">
         <is>
@@ -8991,20 +8975,20 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>abril 2020</t>
+          <t>fevereiro 2020</t>
         </is>
       </c>
       <c r="D232" t="n">
-        <v>352600</v>
+        <v>348801</v>
       </c>
       <c r="E232" t="n">
-        <v>352600</v>
+        <v>348801</v>
       </c>
       <c r="F232" t="n">
-        <v>3515300</v>
+        <v>3308937</v>
       </c>
       <c r="G232" t="n">
-        <v>9970</v>
+        <v>9487</v>
       </c>
       <c r="H232" t="inlineStr">
         <is>
@@ -9013,13 +8997,13 @@
       </c>
       <c r="I232" t="inlineStr">
         <is>
-          <t>2020-04</t>
+          <t>2020-02</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" s="1" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B233" t="inlineStr">
         <is>
@@ -9028,20 +9012,20 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>maio 2020</t>
+          <t>março 2020</t>
         </is>
       </c>
       <c r="D233" t="n">
-        <v>352600</v>
+        <v>351971</v>
       </c>
       <c r="E233" t="n">
-        <v>352600</v>
+        <v>351971</v>
       </c>
       <c r="F233" t="n">
-        <v>3533700</v>
+        <v>3453339</v>
       </c>
       <c r="G233" t="n">
-        <v>10022</v>
+        <v>9811</v>
       </c>
       <c r="H233" t="inlineStr">
         <is>
@@ -9050,13 +9034,13 @@
       </c>
       <c r="I233" t="inlineStr">
         <is>
-          <t>2020-05</t>
+          <t>2020-03</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" s="1" t="n">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="B234" t="inlineStr">
         <is>
@@ -9065,7 +9049,7 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>junho 2020</t>
+          <t>abril 2020</t>
         </is>
       </c>
       <c r="D234" t="n">
@@ -9075,10 +9059,10 @@
         <v>352600</v>
       </c>
       <c r="F234" t="n">
-        <v>3534500</v>
+        <v>3515300</v>
       </c>
       <c r="G234" t="n">
-        <v>10024</v>
+        <v>9970</v>
       </c>
       <c r="H234" t="inlineStr">
         <is>
@@ -9087,13 +9071,13 @@
       </c>
       <c r="I234" t="inlineStr">
         <is>
-          <t>2020-06</t>
+          <t>2020-04</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" s="1" t="n">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B235" t="inlineStr">
         <is>
@@ -9102,20 +9086,20 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>julho 2020</t>
+          <t>maio 2020</t>
         </is>
       </c>
       <c r="D235" t="n">
-        <v>354100</v>
+        <v>352600</v>
       </c>
       <c r="E235" t="n">
-        <v>354100</v>
+        <v>352600</v>
       </c>
       <c r="F235" t="n">
-        <v>3550900</v>
+        <v>3533700</v>
       </c>
       <c r="G235" t="n">
-        <v>10028</v>
+        <v>10022</v>
       </c>
       <c r="H235" t="inlineStr">
         <is>
@@ -9124,13 +9108,13 @@
       </c>
       <c r="I235" t="inlineStr">
         <is>
-          <t>2020-07</t>
+          <t>2020-05</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" s="1" t="n">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B236" t="inlineStr">
         <is>
@@ -9139,20 +9123,20 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>agosto 2020</t>
+          <t>junho 2020</t>
         </is>
       </c>
       <c r="D236" t="n">
-        <v>355900</v>
+        <v>352600</v>
       </c>
       <c r="E236" t="n">
-        <v>355900</v>
+        <v>352600</v>
       </c>
       <c r="F236" t="n">
-        <v>3564900</v>
+        <v>3534500</v>
       </c>
       <c r="G236" t="n">
-        <v>10017</v>
+        <v>10024</v>
       </c>
       <c r="H236" t="inlineStr">
         <is>
@@ -9161,13 +9145,13 @@
       </c>
       <c r="I236" t="inlineStr">
         <is>
-          <t>2020-08</t>
+          <t>2020-06</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" s="1" t="n">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="B237" t="inlineStr">
         <is>
@@ -9176,20 +9160,20 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>setembro 2020</t>
+          <t>julho 2020</t>
         </is>
       </c>
       <c r="D237" t="n">
-        <v>355900</v>
+        <v>354100</v>
       </c>
       <c r="E237" t="n">
-        <v>355900</v>
+        <v>354100</v>
       </c>
       <c r="F237" t="n">
-        <v>3564900</v>
+        <v>3550900</v>
       </c>
       <c r="G237" t="n">
-        <v>10017</v>
+        <v>10028</v>
       </c>
       <c r="H237" t="inlineStr">
         <is>
@@ -9198,13 +9182,13 @@
       </c>
       <c r="I237" t="inlineStr">
         <is>
-          <t>2020-09</t>
+          <t>2020-07</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" s="1" t="n">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B238" t="inlineStr">
         <is>
@@ -9213,7 +9197,7 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>outubro 2020</t>
+          <t>agosto 2020</t>
         </is>
       </c>
       <c r="D238" t="n">
@@ -9235,13 +9219,13 @@
       </c>
       <c r="I238" t="inlineStr">
         <is>
-          <t>2020-10</t>
+          <t>2020-08</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" s="1" t="n">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="B239" t="inlineStr">
         <is>
@@ -9250,7 +9234,7 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>novembro 2020</t>
+          <t>setembro 2020</t>
         </is>
       </c>
       <c r="D239" t="n">
@@ -9272,13 +9256,13 @@
       </c>
       <c r="I239" t="inlineStr">
         <is>
-          <t>2020-11</t>
+          <t>2020-09</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" s="1" t="n">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B240" t="inlineStr">
         <is>
@@ -9287,7 +9271,7 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>dezembro 2020</t>
+          <t>outubro 2020</t>
         </is>
       </c>
       <c r="D240" t="n">
@@ -9309,13 +9293,13 @@
       </c>
       <c r="I240" t="inlineStr">
         <is>
-          <t>2020-12</t>
+          <t>2020-10</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" s="1" t="n">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="B241" t="inlineStr">
         <is>
@@ -9324,20 +9308,20 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>janeiro 2021</t>
+          <t>novembro 2020</t>
         </is>
       </c>
       <c r="D241" t="n">
-        <v>358700</v>
+        <v>355900</v>
       </c>
       <c r="E241" t="n">
-        <v>358700</v>
+        <v>355900</v>
       </c>
       <c r="F241" t="n">
-        <v>3365200</v>
+        <v>3564900</v>
       </c>
       <c r="G241" t="n">
-        <v>9382</v>
+        <v>10017</v>
       </c>
       <c r="H241" t="inlineStr">
         <is>
@@ -9346,13 +9330,13 @@
       </c>
       <c r="I241" t="inlineStr">
         <is>
-          <t>2021-01</t>
+          <t>2020-11</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" s="1" t="n">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="B242" t="inlineStr">
         <is>
@@ -9361,20 +9345,20 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>fevereiro 2021</t>
+          <t>dezembro 2020</t>
         </is>
       </c>
       <c r="D242" t="n">
-        <v>359700</v>
+        <v>355900</v>
       </c>
       <c r="E242" t="n">
-        <v>359700</v>
+        <v>355900</v>
       </c>
       <c r="F242" t="n">
-        <v>3171000</v>
+        <v>3564900</v>
       </c>
       <c r="G242" t="n">
-        <v>8816</v>
+        <v>10017</v>
       </c>
       <c r="H242" t="inlineStr">
         <is>
@@ -9383,13 +9367,13 @@
       </c>
       <c r="I242" t="inlineStr">
         <is>
-          <t>2021-02</t>
+          <t>2020-12</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" s="1" t="n">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="B243" t="inlineStr">
         <is>
@@ -9398,20 +9382,20 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>março 2021</t>
+          <t>janeiro 2021</t>
         </is>
       </c>
       <c r="D243" t="n">
-        <v>362700</v>
+        <v>358700</v>
       </c>
       <c r="E243" t="n">
-        <v>362700</v>
+        <v>358700</v>
       </c>
       <c r="F243" t="n">
-        <v>3072800</v>
+        <v>3365200</v>
       </c>
       <c r="G243" t="n">
-        <v>8472</v>
+        <v>9382</v>
       </c>
       <c r="H243" t="inlineStr">
         <is>
@@ -9420,13 +9404,13 @@
       </c>
       <c r="I243" t="inlineStr">
         <is>
-          <t>2021-03</t>
+          <t>2021-01</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" s="1" t="n">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B244" t="inlineStr">
         <is>
@@ -9435,20 +9419,20 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>abril 2021</t>
+          <t>fevereiro 2021</t>
         </is>
       </c>
       <c r="D244" t="n">
-        <v>372000</v>
+        <v>359700</v>
       </c>
       <c r="E244" t="n">
-        <v>372000</v>
+        <v>359700</v>
       </c>
       <c r="F244" t="n">
-        <v>3120100</v>
+        <v>3171000</v>
       </c>
       <c r="G244" t="n">
-        <v>8387</v>
+        <v>8816</v>
       </c>
       <c r="H244" t="inlineStr">
         <is>
@@ -9457,13 +9441,13 @@
       </c>
       <c r="I244" t="inlineStr">
         <is>
-          <t>2021-04</t>
+          <t>2021-02</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" s="1" t="n">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="B245" t="inlineStr">
         <is>
@@ -9472,20 +9456,20 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>maio 2021</t>
+          <t>março 2021</t>
         </is>
       </c>
       <c r="D245" t="n">
-        <v>372000</v>
+        <v>362700</v>
       </c>
       <c r="E245" t="n">
-        <v>372000</v>
+        <v>362700</v>
       </c>
       <c r="F245" t="n">
-        <v>3116700</v>
+        <v>3072800</v>
       </c>
       <c r="G245" t="n">
-        <v>8378</v>
+        <v>8472</v>
       </c>
       <c r="H245" t="inlineStr">
         <is>
@@ -9494,13 +9478,13 @@
       </c>
       <c r="I245" t="inlineStr">
         <is>
-          <t>2021-05</t>
+          <t>2021-03</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" s="1" t="n">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="B246" t="inlineStr">
         <is>
@@ -9509,7 +9493,7 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>junho 2021</t>
+          <t>abril 2021</t>
         </is>
       </c>
       <c r="D246" t="n">
@@ -9519,10 +9503,10 @@
         <v>372000</v>
       </c>
       <c r="F246" t="n">
-        <v>3103900</v>
+        <v>3120100</v>
       </c>
       <c r="G246" t="n">
-        <v>8344</v>
+        <v>8387</v>
       </c>
       <c r="H246" t="inlineStr">
         <is>
@@ -9531,13 +9515,13 @@
       </c>
       <c r="I246" t="inlineStr">
         <is>
-          <t>2021-06</t>
+          <t>2021-04</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" s="1" t="n">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="B247" t="inlineStr">
         <is>
@@ -9546,20 +9530,20 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>julho 2021</t>
+          <t>maio 2021</t>
         </is>
       </c>
       <c r="D247" t="n">
-        <v>370600</v>
+        <v>372000</v>
       </c>
       <c r="E247" t="n">
-        <v>370600</v>
+        <v>372000</v>
       </c>
       <c r="F247" t="n">
-        <v>3803700</v>
+        <v>3116700</v>
       </c>
       <c r="G247" t="n">
-        <v>10264</v>
+        <v>8378</v>
       </c>
       <c r="H247" t="inlineStr">
         <is>
@@ -9568,13 +9552,13 @@
       </c>
       <c r="I247" t="inlineStr">
         <is>
-          <t>2021-07</t>
+          <t>2021-05</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" s="1" t="n">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="B248" t="inlineStr">
         <is>
@@ -9583,20 +9567,20 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>agosto 2021</t>
+          <t>junho 2021</t>
         </is>
       </c>
       <c r="D248" t="n">
-        <v>372500</v>
+        <v>372000</v>
       </c>
       <c r="E248" t="n">
-        <v>372500</v>
+        <v>372000</v>
       </c>
       <c r="F248" t="n">
-        <v>3115200</v>
+        <v>3103900</v>
       </c>
       <c r="G248" t="n">
-        <v>8363</v>
+        <v>8344</v>
       </c>
       <c r="H248" t="inlineStr">
         <is>
@@ -9605,13 +9589,13 @@
       </c>
       <c r="I248" t="inlineStr">
         <is>
-          <t>2021-08</t>
+          <t>2021-06</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" s="1" t="n">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="B249" t="inlineStr">
         <is>
@@ -9620,20 +9604,20 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>setembro 2021</t>
+          <t>julho 2021</t>
         </is>
       </c>
       <c r="D249" t="n">
-        <v>372500</v>
+        <v>370600</v>
       </c>
       <c r="E249" t="n">
-        <v>372500</v>
+        <v>370600</v>
       </c>
       <c r="F249" t="n">
-        <v>3115200</v>
+        <v>3803700</v>
       </c>
       <c r="G249" t="n">
-        <v>8363</v>
+        <v>10264</v>
       </c>
       <c r="H249" t="inlineStr">
         <is>
@@ -9642,13 +9626,13 @@
       </c>
       <c r="I249" t="inlineStr">
         <is>
-          <t>2021-09</t>
+          <t>2021-07</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" s="1" t="n">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="B250" t="inlineStr">
         <is>
@@ -9657,7 +9641,7 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>outubro 2021</t>
+          <t>agosto 2021</t>
         </is>
       </c>
       <c r="D250" t="n">
@@ -9679,13 +9663,13 @@
       </c>
       <c r="I250" t="inlineStr">
         <is>
-          <t>2021-10</t>
+          <t>2021-08</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" s="1" t="n">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="B251" t="inlineStr">
         <is>
@@ -9694,17 +9678,17 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>novembro 2021</t>
+          <t>setembro 2021</t>
         </is>
       </c>
       <c r="D251" t="n">
-        <v>372700</v>
+        <v>372500</v>
       </c>
       <c r="E251" t="n">
-        <v>372700</v>
+        <v>372500</v>
       </c>
       <c r="F251" t="n">
-        <v>3116800</v>
+        <v>3115200</v>
       </c>
       <c r="G251" t="n">
         <v>8363</v>
@@ -9716,13 +9700,13 @@
       </c>
       <c r="I251" t="inlineStr">
         <is>
-          <t>2021-11</t>
+          <t>2021-09</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" s="1" t="n">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B252" t="inlineStr">
         <is>
@@ -9731,17 +9715,17 @@
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>dezembro 2021</t>
+          <t>outubro 2021</t>
         </is>
       </c>
       <c r="D252" t="n">
-        <v>372700</v>
+        <v>372500</v>
       </c>
       <c r="E252" t="n">
-        <v>372700</v>
+        <v>372500</v>
       </c>
       <c r="F252" t="n">
-        <v>3116800</v>
+        <v>3115200</v>
       </c>
       <c r="G252" t="n">
         <v>8363</v>
@@ -9753,13 +9737,13 @@
       </c>
       <c r="I252" t="inlineStr">
         <is>
-          <t>2021-12</t>
+          <t>2021-10</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" s="1" t="n">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="B253" t="inlineStr">
         <is>
@@ -9768,20 +9752,20 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>janeiro 2022</t>
+          <t>novembro 2021</t>
         </is>
       </c>
       <c r="D253" t="n">
-        <v>437500</v>
+        <v>372700</v>
       </c>
       <c r="E253" t="n">
-        <v>437500</v>
+        <v>372700</v>
       </c>
       <c r="F253" t="n">
-        <v>2726600</v>
+        <v>3116800</v>
       </c>
       <c r="G253" t="n">
-        <v>6232</v>
+        <v>8363</v>
       </c>
       <c r="H253" t="inlineStr">
         <is>
@@ -9790,13 +9774,13 @@
       </c>
       <c r="I253" t="inlineStr">
         <is>
-          <t>2022-01</t>
+          <t>2021-11</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" s="1" t="n">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="B254" t="inlineStr">
         <is>
@@ -9805,20 +9789,20 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>fevereiro 2022</t>
+          <t>dezembro 2021</t>
         </is>
       </c>
       <c r="D254" t="n">
-        <v>434200</v>
+        <v>372700</v>
       </c>
       <c r="E254" t="n">
-        <v>434200</v>
+        <v>372700</v>
       </c>
       <c r="F254" t="n">
-        <v>2764600</v>
+        <v>3116800</v>
       </c>
       <c r="G254" t="n">
-        <v>6367</v>
+        <v>8363</v>
       </c>
       <c r="H254" t="inlineStr">
         <is>
@@ -9827,13 +9811,13 @@
       </c>
       <c r="I254" t="inlineStr">
         <is>
-          <t>2022-02</t>
+          <t>2021-12</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" s="1" t="n">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="B255" t="inlineStr">
         <is>
@@ -9842,20 +9826,20 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>março 2022</t>
+          <t>janeiro 2022</t>
         </is>
       </c>
       <c r="D255" t="n">
-        <v>433371</v>
+        <v>437500</v>
       </c>
       <c r="E255" t="n">
-        <v>433371</v>
+        <v>437500</v>
       </c>
       <c r="F255" t="n">
-        <v>2892905</v>
+        <v>2726600</v>
       </c>
       <c r="G255" t="n">
-        <v>6675</v>
+        <v>6232</v>
       </c>
       <c r="H255" t="inlineStr">
         <is>
@@ -9864,13 +9848,13 @@
       </c>
       <c r="I255" t="inlineStr">
         <is>
-          <t>2022-03</t>
+          <t>2022-01</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" s="1" t="n">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="B256" t="inlineStr">
         <is>
@@ -9879,20 +9863,20 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>abril 2022</t>
+          <t>fevereiro 2022</t>
         </is>
       </c>
       <c r="D256" t="n">
-        <v>433700</v>
+        <v>434200</v>
       </c>
       <c r="E256" t="n">
-        <v>433700</v>
+        <v>434200</v>
       </c>
       <c r="F256" t="n">
-        <v>2941400</v>
+        <v>2764600</v>
       </c>
       <c r="G256" t="n">
-        <v>6782</v>
+        <v>6367</v>
       </c>
       <c r="H256" t="inlineStr">
         <is>
@@ -9901,13 +9885,13 @@
       </c>
       <c r="I256" t="inlineStr">
         <is>
-          <t>2022-04</t>
+          <t>2022-02</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" s="1" t="n">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="B257" t="inlineStr">
         <is>
@@ -9916,20 +9900,20 @@
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>maio 2022</t>
+          <t>março 2022</t>
         </is>
       </c>
       <c r="D257" t="n">
-        <v>432900</v>
+        <v>433371</v>
       </c>
       <c r="E257" t="n">
-        <v>432900</v>
+        <v>433371</v>
       </c>
       <c r="F257" t="n">
-        <v>2969800</v>
+        <v>2892905</v>
       </c>
       <c r="G257" t="n">
-        <v>6860</v>
+        <v>6675</v>
       </c>
       <c r="H257" t="inlineStr">
         <is>
@@ -9938,13 +9922,13 @@
       </c>
       <c r="I257" t="inlineStr">
         <is>
-          <t>2022-05</t>
+          <t>2022-03</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" s="1" t="n">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="B258" t="inlineStr">
         <is>
@@ -9953,20 +9937,20 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>junho 2022</t>
+          <t>abril 2022</t>
         </is>
       </c>
       <c r="D258" t="n">
-        <v>431700</v>
+        <v>433700</v>
       </c>
       <c r="E258" t="n">
-        <v>431700</v>
+        <v>433700</v>
       </c>
       <c r="F258" t="n">
-        <v>2970700</v>
+        <v>2941400</v>
       </c>
       <c r="G258" t="n">
-        <v>6881</v>
+        <v>6782</v>
       </c>
       <c r="H258" t="inlineStr">
         <is>
@@ -9975,13 +9959,13 @@
       </c>
       <c r="I258" t="inlineStr">
         <is>
-          <t>2022-06</t>
+          <t>2022-04</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" s="1" t="n">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="B259" t="inlineStr">
         <is>
@@ -9990,20 +9974,20 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>julho 2022</t>
+          <t>maio 2022</t>
         </is>
       </c>
       <c r="D259" t="n">
-        <v>432000</v>
+        <v>432900</v>
       </c>
       <c r="E259" t="n">
-        <v>432000</v>
+        <v>432900</v>
       </c>
       <c r="F259" t="n">
-        <v>2973200</v>
+        <v>2969800</v>
       </c>
       <c r="G259" t="n">
-        <v>6882</v>
+        <v>6860</v>
       </c>
       <c r="H259" t="inlineStr">
         <is>
@@ -10012,13 +9996,13 @@
       </c>
       <c r="I259" t="inlineStr">
         <is>
-          <t>2022-07</t>
+          <t>2022-05</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" s="1" t="n">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="B260" t="inlineStr">
         <is>
@@ -10027,20 +10011,20 @@
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>agosto 2022</t>
+          <t>junho 2022</t>
         </is>
       </c>
       <c r="D260" t="n">
-        <v>432000</v>
+        <v>431700</v>
       </c>
       <c r="E260" t="n">
-        <v>432000</v>
+        <v>431700</v>
       </c>
       <c r="F260" t="n">
-        <v>2961900</v>
+        <v>2970700</v>
       </c>
       <c r="G260" t="n">
-        <v>6856</v>
+        <v>6881</v>
       </c>
       <c r="H260" t="inlineStr">
         <is>
@@ -10049,13 +10033,13 @@
       </c>
       <c r="I260" t="inlineStr">
         <is>
-          <t>2022-08</t>
+          <t>2022-06</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" s="1" t="n">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="B261" t="inlineStr">
         <is>
@@ -10064,20 +10048,20 @@
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>setembro 2022</t>
+          <t>julho 2022</t>
         </is>
       </c>
       <c r="D261" t="n">
-        <v>431470</v>
+        <v>432000</v>
       </c>
       <c r="E261" t="n">
-        <v>431470</v>
+        <v>432000</v>
       </c>
       <c r="F261" t="n">
-        <v>2961944</v>
+        <v>2973200</v>
       </c>
       <c r="G261" t="n">
-        <v>6865</v>
+        <v>6882</v>
       </c>
       <c r="H261" t="inlineStr">
         <is>
@@ -10086,13 +10070,13 @@
       </c>
       <c r="I261" t="inlineStr">
         <is>
-          <t>2022-09</t>
+          <t>2022-07</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" s="1" t="n">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="B262" t="inlineStr">
         <is>
@@ -10101,20 +10085,20 @@
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>outubro 2022</t>
+          <t>agosto 2022</t>
         </is>
       </c>
       <c r="D262" t="n">
-        <v>432100</v>
+        <v>432000</v>
       </c>
       <c r="E262" t="n">
-        <v>432100</v>
+        <v>432000</v>
       </c>
       <c r="F262" t="n">
-        <v>2963800</v>
+        <v>2961900</v>
       </c>
       <c r="G262" t="n">
-        <v>6859</v>
+        <v>6856</v>
       </c>
       <c r="H262" t="inlineStr">
         <is>
@@ -10123,13 +10107,13 @@
       </c>
       <c r="I262" t="inlineStr">
         <is>
-          <t>2022-10</t>
+          <t>2022-08</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" s="1" t="n">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="B263" t="inlineStr">
         <is>
@@ -10138,20 +10122,20 @@
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>novembro 2022</t>
+          <t>setembro 2022</t>
         </is>
       </c>
       <c r="D263" t="n">
-        <v>432100</v>
+        <v>431470</v>
       </c>
       <c r="E263" t="n">
-        <v>432100</v>
+        <v>431470</v>
       </c>
       <c r="F263" t="n">
-        <v>2963800</v>
+        <v>2961944</v>
       </c>
       <c r="G263" t="n">
-        <v>6859</v>
+        <v>6865</v>
       </c>
       <c r="H263" t="inlineStr">
         <is>
@@ -10160,13 +10144,13 @@
       </c>
       <c r="I263" t="inlineStr">
         <is>
-          <t>2022-11</t>
+          <t>2022-09</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" s="1" t="n">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="B264" t="inlineStr">
         <is>
@@ -10175,7 +10159,7 @@
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>dezembro 2022</t>
+          <t>outubro 2022</t>
         </is>
       </c>
       <c r="D264" t="n">
@@ -10197,13 +10181,13 @@
       </c>
       <c r="I264" t="inlineStr">
         <is>
-          <t>2022-12</t>
+          <t>2022-10</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" s="1" t="n">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="B265" t="inlineStr">
         <is>
@@ -10212,20 +10196,20 @@
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>janeiro 2023</t>
+          <t>novembro 2022</t>
         </is>
       </c>
       <c r="D265" t="n">
-        <v>386700</v>
+        <v>432100</v>
       </c>
       <c r="E265" t="n">
-        <v>386700</v>
+        <v>432100</v>
       </c>
       <c r="F265" t="n">
-        <v>3692500</v>
+        <v>2963800</v>
       </c>
       <c r="G265" t="n">
-        <v>9549</v>
+        <v>6859</v>
       </c>
       <c r="H265" t="inlineStr">
         <is>
@@ -10234,13 +10218,13 @@
       </c>
       <c r="I265" t="inlineStr">
         <is>
-          <t>2023-01</t>
+          <t>2022-11</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" s="1" t="n">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="B266" t="inlineStr">
         <is>
@@ -10249,20 +10233,20 @@
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>fevereiro 2023</t>
+          <t>dezembro 2022</t>
         </is>
       </c>
       <c r="D266" t="n">
-        <v>386485</v>
+        <v>432100</v>
       </c>
       <c r="E266" t="n">
-        <v>386485</v>
+        <v>432100</v>
       </c>
       <c r="F266" t="n">
-        <v>3696422</v>
+        <v>2963800</v>
       </c>
       <c r="G266" t="n">
-        <v>9564</v>
+        <v>6859</v>
       </c>
       <c r="H266" t="inlineStr">
         <is>
@@ -10271,13 +10255,13 @@
       </c>
       <c r="I266" t="inlineStr">
         <is>
-          <t>2023-02</t>
+          <t>2022-12</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" s="1" t="n">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="B267" t="inlineStr">
         <is>
@@ -10286,20 +10270,20 @@
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>março 2023</t>
+          <t>janeiro 2023</t>
         </is>
       </c>
       <c r="D267" t="n">
-        <v>387200</v>
+        <v>386700</v>
       </c>
       <c r="E267" t="n">
-        <v>387200</v>
+        <v>386700</v>
       </c>
       <c r="F267" t="n">
-        <v>3758800</v>
+        <v>3692500</v>
       </c>
       <c r="G267" t="n">
-        <v>9708</v>
+        <v>9549</v>
       </c>
       <c r="H267" t="inlineStr">
         <is>
@@ -10308,13 +10292,13 @@
       </c>
       <c r="I267" t="inlineStr">
         <is>
-          <t>2023-03</t>
+          <t>2023-01</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" s="1" t="n">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="B268" t="inlineStr">
         <is>
@@ -10323,20 +10307,20 @@
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>abril 2023</t>
+          <t>fevereiro 2023</t>
         </is>
       </c>
       <c r="D268" t="n">
-        <v>385800</v>
+        <v>386485</v>
       </c>
       <c r="E268" t="n">
-        <v>385800</v>
+        <v>386485</v>
       </c>
       <c r="F268" t="n">
-        <v>3793000</v>
+        <v>3696422</v>
       </c>
       <c r="G268" t="n">
-        <v>9832</v>
+        <v>9564</v>
       </c>
       <c r="H268" t="inlineStr">
         <is>
@@ -10345,13 +10329,13 @@
       </c>
       <c r="I268" t="inlineStr">
         <is>
-          <t>2023-04</t>
+          <t>2023-02</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" s="1" t="n">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="B269" t="inlineStr">
         <is>
@@ -10360,20 +10344,20 @@
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>maio 2023</t>
+          <t>março 2023</t>
         </is>
       </c>
       <c r="D269" t="n">
-        <v>385300</v>
+        <v>387200</v>
       </c>
       <c r="E269" t="n">
-        <v>385300</v>
+        <v>387200</v>
       </c>
       <c r="F269" t="n">
-        <v>3827500</v>
+        <v>3758800</v>
       </c>
       <c r="G269" t="n">
-        <v>9934</v>
+        <v>9708</v>
       </c>
       <c r="H269" t="inlineStr">
         <is>
@@ -10382,13 +10366,13 @@
       </c>
       <c r="I269" t="inlineStr">
         <is>
-          <t>2023-05</t>
+          <t>2023-03</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" s="1" t="n">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="B270" t="inlineStr">
         <is>
@@ -10397,20 +10381,20 @@
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>junho 2023</t>
+          <t>abril 2023</t>
         </is>
       </c>
       <c r="D270" t="n">
-        <v>385300</v>
+        <v>385800</v>
       </c>
       <c r="E270" t="n">
-        <v>385300</v>
+        <v>385800</v>
       </c>
       <c r="F270" t="n">
-        <v>3827500</v>
+        <v>3793000</v>
       </c>
       <c r="G270" t="n">
-        <v>9934</v>
+        <v>9832</v>
       </c>
       <c r="H270" t="inlineStr">
         <is>
@@ -10419,13 +10403,13 @@
       </c>
       <c r="I270" t="inlineStr">
         <is>
-          <t>2023-06</t>
+          <t>2023-04</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" s="1" t="n">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="B271" t="inlineStr">
         <is>
@@ -10434,20 +10418,20 @@
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>julho 2023</t>
+          <t>maio 2023</t>
         </is>
       </c>
       <c r="D271" t="n">
-        <v>384700</v>
+        <v>385300</v>
       </c>
       <c r="E271" t="n">
-        <v>384700</v>
+        <v>385300</v>
       </c>
       <c r="F271" t="n">
-        <v>3817800</v>
+        <v>3827500</v>
       </c>
       <c r="G271" t="n">
-        <v>9924</v>
+        <v>9934</v>
       </c>
       <c r="H271" t="inlineStr">
         <is>
@@ -10456,13 +10440,13 @@
       </c>
       <c r="I271" t="inlineStr">
         <is>
-          <t>2023-07</t>
+          <t>2023-05</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" s="1" t="n">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="B272" t="inlineStr">
         <is>
@@ -10471,20 +10455,20 @@
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>agosto 2023</t>
+          <t>junho 2023</t>
         </is>
       </c>
       <c r="D272" t="n">
-        <v>379100</v>
+        <v>385300</v>
       </c>
       <c r="E272" t="n">
-        <v>379100</v>
+        <v>385300</v>
       </c>
       <c r="F272" t="n">
-        <v>3786800</v>
+        <v>3827500</v>
       </c>
       <c r="G272" t="n">
-        <v>9989</v>
+        <v>9934</v>
       </c>
       <c r="H272" t="inlineStr">
         <is>
@@ -10493,13 +10477,13 @@
       </c>
       <c r="I272" t="inlineStr">
         <is>
-          <t>2023-08</t>
+          <t>2023-06</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" s="1" t="n">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="B273" t="inlineStr">
         <is>
@@ -10508,20 +10492,20 @@
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>setembro 2023</t>
+          <t>julho 2023</t>
         </is>
       </c>
       <c r="D273" t="n">
-        <v>379100</v>
+        <v>384700</v>
       </c>
       <c r="E273" t="n">
-        <v>379100</v>
+        <v>384700</v>
       </c>
       <c r="F273" t="n">
-        <v>3784700</v>
+        <v>3817800</v>
       </c>
       <c r="G273" t="n">
-        <v>9983</v>
+        <v>9924</v>
       </c>
       <c r="H273" t="inlineStr">
         <is>
@@ -10530,13 +10514,13 @@
       </c>
       <c r="I273" t="inlineStr">
         <is>
-          <t>2023-09</t>
+          <t>2023-07</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" s="1" t="n">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="B274" t="inlineStr">
         <is>
@@ -10545,7 +10529,7 @@
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>outubro 2023</t>
+          <t>agosto 2023</t>
         </is>
       </c>
       <c r="D274" t="n">
@@ -10555,10 +10539,10 @@
         <v>379100</v>
       </c>
       <c r="F274" t="n">
-        <v>3783500</v>
+        <v>3786800</v>
       </c>
       <c r="G274" t="n">
-        <v>9980</v>
+        <v>9989</v>
       </c>
       <c r="H274" t="inlineStr">
         <is>
@@ -10567,13 +10551,13 @@
       </c>
       <c r="I274" t="inlineStr">
         <is>
-          <t>2023-10</t>
+          <t>2023-08</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" s="1" t="n">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="B275" t="inlineStr">
         <is>
@@ -10582,7 +10566,7 @@
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>novembro 2023</t>
+          <t>setembro 2023</t>
         </is>
       </c>
       <c r="D275" t="n">
@@ -10592,10 +10576,10 @@
         <v>379100</v>
       </c>
       <c r="F275" t="n">
-        <v>3783500</v>
+        <v>3784700</v>
       </c>
       <c r="G275" t="n">
-        <v>9980</v>
+        <v>9983</v>
       </c>
       <c r="H275" t="inlineStr">
         <is>
@@ -10604,13 +10588,13 @@
       </c>
       <c r="I275" t="inlineStr">
         <is>
-          <t>2023-11</t>
+          <t>2023-09</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" s="1" t="n">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B276" t="inlineStr">
         <is>
@@ -10619,7 +10603,7 @@
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>dezembro 2023</t>
+          <t>outubro 2023</t>
         </is>
       </c>
       <c r="D276" t="n">
@@ -10629,10 +10613,10 @@
         <v>379100</v>
       </c>
       <c r="F276" t="n">
-        <v>3782300</v>
+        <v>3783500</v>
       </c>
       <c r="G276" t="n">
-        <v>9977</v>
+        <v>9980</v>
       </c>
       <c r="H276" t="inlineStr">
         <is>
@@ -10641,13 +10625,13 @@
       </c>
       <c r="I276" t="inlineStr">
         <is>
-          <t>2023-12</t>
+          <t>2023-10</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" s="1" t="n">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="B277" t="inlineStr">
         <is>
@@ -10656,20 +10640,20 @@
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>janeiro 2024</t>
+          <t>novembro 2023</t>
         </is>
       </c>
       <c r="D277" t="n">
-        <v>291500</v>
+        <v>379100</v>
       </c>
       <c r="E277" t="n">
-        <v>291500</v>
+        <v>379100</v>
       </c>
       <c r="F277" t="n">
-        <v>2611900</v>
+        <v>3783500</v>
       </c>
       <c r="G277" t="n">
-        <v>8960</v>
+        <v>9980</v>
       </c>
       <c r="H277" t="inlineStr">
         <is>
@@ -10678,13 +10662,13 @@
       </c>
       <c r="I277" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2023-11</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" s="1" t="n">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="B278" t="inlineStr">
         <is>
@@ -10693,20 +10677,20 @@
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>fevereiro 2024</t>
+          <t>dezembro 2023</t>
         </is>
       </c>
       <c r="D278" t="n">
-        <v>296500</v>
+        <v>379100</v>
       </c>
       <c r="E278" t="n">
-        <v>296500</v>
+        <v>379100</v>
       </c>
       <c r="F278" t="n">
-        <v>2591500</v>
+        <v>3782300</v>
       </c>
       <c r="G278" t="n">
-        <v>8740</v>
+        <v>9977</v>
       </c>
       <c r="H278" t="inlineStr">
         <is>
@@ -10715,13 +10699,13 @@
       </c>
       <c r="I278" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2023-12</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" s="1" t="n">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="B279" t="inlineStr">
         <is>
@@ -10730,20 +10714,20 @@
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>março 2024</t>
+          <t>janeiro 2024</t>
         </is>
       </c>
       <c r="D279" t="n">
-        <v>296700</v>
+        <v>291500</v>
       </c>
       <c r="E279" t="n">
-        <v>296700</v>
+        <v>291500</v>
       </c>
       <c r="F279" t="n">
-        <v>2548600</v>
+        <v>2611900</v>
       </c>
       <c r="G279" t="n">
-        <v>8590</v>
+        <v>8960</v>
       </c>
       <c r="H279" t="inlineStr">
         <is>
@@ -10752,13 +10736,13 @@
       </c>
       <c r="I279" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-01</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" s="1" t="n">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="B280" t="inlineStr">
         <is>
@@ -10767,20 +10751,20 @@
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>abril 2024</t>
+          <t>fevereiro 2024</t>
         </is>
       </c>
       <c r="D280" t="n">
-        <v>296300</v>
+        <v>296500</v>
       </c>
       <c r="E280" t="n">
-        <v>296300</v>
+        <v>296500</v>
       </c>
       <c r="F280" t="n">
-        <v>2526600</v>
+        <v>2591500</v>
       </c>
       <c r="G280" t="n">
-        <v>8527</v>
+        <v>8740</v>
       </c>
       <c r="H280" t="inlineStr">
         <is>
@@ -10789,13 +10773,13 @@
       </c>
       <c r="I280" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-02</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" s="1" t="n">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="B281" t="inlineStr">
         <is>
@@ -10804,20 +10788,20 @@
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>maio 2024</t>
+          <t>março 2024</t>
         </is>
       </c>
       <c r="D281" t="n">
-        <v>296400</v>
+        <v>296700</v>
       </c>
       <c r="E281" t="n">
-        <v>296400</v>
+        <v>296700</v>
       </c>
       <c r="F281" t="n">
-        <v>2552800</v>
+        <v>2548600</v>
       </c>
       <c r="G281" t="n">
-        <v>8613</v>
+        <v>8590</v>
       </c>
       <c r="H281" t="inlineStr">
         <is>
@@ -10826,13 +10810,13 @@
       </c>
       <c r="I281" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-03</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" s="1" t="n">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="B282" t="inlineStr">
         <is>
@@ -10841,20 +10825,20 @@
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>junho 2024</t>
+          <t>abril 2024</t>
         </is>
       </c>
       <c r="D282" t="n">
-        <v>297200</v>
+        <v>296300</v>
       </c>
       <c r="E282" t="n">
-        <v>297200</v>
+        <v>296300</v>
       </c>
       <c r="F282" t="n">
-        <v>2555600</v>
+        <v>2526600</v>
       </c>
       <c r="G282" t="n">
-        <v>8599</v>
+        <v>8527</v>
       </c>
       <c r="H282" t="inlineStr">
         <is>
@@ -10863,13 +10847,13 @@
       </c>
       <c r="I282" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2024-04</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" s="1" t="n">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="B283" t="inlineStr">
         <is>
@@ -10878,20 +10862,20 @@
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>julho 2024</t>
+          <t>maio 2024</t>
         </is>
       </c>
       <c r="D283" t="n">
-        <v>296000</v>
+        <v>296400</v>
       </c>
       <c r="E283" t="n">
-        <v>296000</v>
+        <v>296400</v>
       </c>
       <c r="F283" t="n">
-        <v>2543000</v>
+        <v>2552800</v>
       </c>
       <c r="G283" t="n">
-        <v>8591</v>
+        <v>8613</v>
       </c>
       <c r="H283" t="inlineStr">
         <is>
@@ -10900,13 +10884,13 @@
       </c>
       <c r="I283" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2024-05</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" s="1" t="n">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="B284" t="inlineStr">
         <is>
@@ -10915,20 +10899,20 @@
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>agosto 2024</t>
+          <t>junho 2024</t>
         </is>
       </c>
       <c r="D284" t="n">
-        <v>296000</v>
+        <v>297200</v>
       </c>
       <c r="E284" t="n">
-        <v>296000</v>
+        <v>297200</v>
       </c>
       <c r="F284" t="n">
-        <v>2543100</v>
+        <v>2555600</v>
       </c>
       <c r="G284" t="n">
-        <v>8592</v>
+        <v>8599</v>
       </c>
       <c r="H284" t="inlineStr">
         <is>
@@ -10937,13 +10921,13 @@
       </c>
       <c r="I284" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2024-06</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" s="1" t="n">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="B285" t="inlineStr">
         <is>
@@ -10952,20 +10936,20 @@
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>setembro 2024</t>
+          <t>julho 2024</t>
         </is>
       </c>
       <c r="D285" t="n">
-        <v>294400</v>
+        <v>296000</v>
       </c>
       <c r="E285" t="n">
-        <v>294400</v>
+        <v>296000</v>
       </c>
       <c r="F285" t="n">
-        <v>2524500</v>
+        <v>2543000</v>
       </c>
       <c r="G285" t="n">
-        <v>8575</v>
+        <v>8591</v>
       </c>
       <c r="H285" t="inlineStr">
         <is>
@@ -10974,13 +10958,13 @@
       </c>
       <c r="I285" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2024-07</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" s="1" t="n">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="B286" t="inlineStr">
         <is>
@@ -10989,20 +10973,20 @@
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>outubro 2024</t>
+          <t>agosto 2024</t>
         </is>
       </c>
       <c r="D286" t="n">
-        <v>294400</v>
+        <v>296000</v>
       </c>
       <c r="E286" t="n">
-        <v>294400</v>
+        <v>296000</v>
       </c>
       <c r="F286" t="n">
-        <v>2524800</v>
+        <v>2543100</v>
       </c>
       <c r="G286" t="n">
-        <v>8576</v>
+        <v>8592</v>
       </c>
       <c r="H286" t="inlineStr">
         <is>
@@ -11011,13 +10995,13 @@
       </c>
       <c r="I286" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2024-08</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" s="1" t="n">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B287" t="inlineStr">
         <is>
@@ -11026,7 +11010,7 @@
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>novembro 2024</t>
+          <t>setembro 2024</t>
         </is>
       </c>
       <c r="D287" t="n">
@@ -11036,10 +11020,10 @@
         <v>294400</v>
       </c>
       <c r="F287" t="n">
-        <v>2525000</v>
+        <v>2524500</v>
       </c>
       <c r="G287" t="n">
-        <v>8577</v>
+        <v>8575</v>
       </c>
       <c r="H287" t="inlineStr">
         <is>
@@ -11048,13 +11032,13 @@
       </c>
       <c r="I287" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2024-09</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" s="1" t="n">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B288" t="inlineStr">
         <is>
@@ -11063,7 +11047,7 @@
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>dezembro 2024</t>
+          <t>outubro 2024</t>
         </is>
       </c>
       <c r="D288" t="n">
@@ -11073,10 +11057,10 @@
         <v>294400</v>
       </c>
       <c r="F288" t="n">
-        <v>2525000</v>
+        <v>2524800</v>
       </c>
       <c r="G288" t="n">
-        <v>8577</v>
+        <v>8576</v>
       </c>
       <c r="H288" t="inlineStr">
         <is>
@@ -11085,13 +11069,13 @@
       </c>
       <c r="I288" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2024-10</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" s="1" t="n">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="B289" t="inlineStr">
         <is>
@@ -11100,20 +11084,20 @@
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>janeiro 2025</t>
+          <t>novembro 2024</t>
         </is>
       </c>
       <c r="D289" t="n">
-        <v>260700</v>
+        <v>294400</v>
       </c>
       <c r="E289" t="n">
-        <v>260700</v>
+        <v>294400</v>
       </c>
       <c r="F289" t="n">
-        <v>2637300</v>
+        <v>2525000</v>
       </c>
       <c r="G289" t="n">
-        <v>10116</v>
+        <v>8577</v>
       </c>
       <c r="H289" t="inlineStr">
         <is>
@@ -11122,13 +11106,13 @@
       </c>
       <c r="I289" t="inlineStr">
         <is>
-          <t>2025-01</t>
+          <t>2024-11</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" s="1" t="n">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="B290" t="inlineStr">
         <is>
@@ -11137,20 +11121,20 @@
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>fevereiro 2025</t>
+          <t>dezembro 2024</t>
         </is>
       </c>
       <c r="D290" t="n">
-        <v>267500</v>
+        <v>294400</v>
       </c>
       <c r="E290" t="n">
-        <v>267500</v>
+        <v>294400</v>
       </c>
       <c r="F290" t="n">
-        <v>2798300</v>
+        <v>2525000</v>
       </c>
       <c r="G290" t="n">
-        <v>10461</v>
+        <v>8577</v>
       </c>
       <c r="H290" t="inlineStr">
         <is>
@@ -11159,13 +11143,13 @@
       </c>
       <c r="I290" t="inlineStr">
         <is>
-          <t>2025-02</t>
+          <t>2024-12</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" s="1" t="n">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="B291" t="inlineStr">
         <is>
@@ -11174,20 +11158,20 @@
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>março 2025</t>
+          <t>janeiro 2025</t>
         </is>
       </c>
       <c r="D291" t="n">
-        <v>268300</v>
+        <v>260700</v>
       </c>
       <c r="E291" t="n">
-        <v>268300</v>
+        <v>260700</v>
       </c>
       <c r="F291" t="n">
-        <v>2851300</v>
+        <v>2637300</v>
       </c>
       <c r="G291" t="n">
-        <v>10627</v>
+        <v>10116</v>
       </c>
       <c r="H291" t="inlineStr">
         <is>
@@ -11196,13 +11180,13 @@
       </c>
       <c r="I291" t="inlineStr">
         <is>
-          <t>2025-03</t>
+          <t>2025-01</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" s="1" t="n">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="B292" t="inlineStr">
         <is>
@@ -11211,20 +11195,20 @@
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>abril 2025</t>
+          <t>fevereiro 2025</t>
         </is>
       </c>
       <c r="D292" t="n">
-        <v>269300</v>
+        <v>267500</v>
       </c>
       <c r="E292" t="n">
-        <v>269300</v>
+        <v>267500</v>
       </c>
       <c r="F292" t="n">
-        <v>2923200</v>
+        <v>2798300</v>
       </c>
       <c r="G292" t="n">
-        <v>10855</v>
+        <v>10461</v>
       </c>
       <c r="H292" t="inlineStr">
         <is>
@@ -11233,13 +11217,13 @@
       </c>
       <c r="I292" t="inlineStr">
         <is>
-          <t>2025-04</t>
+          <t>2025-02</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" s="1" t="n">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="B293" t="inlineStr">
         <is>
@@ -11248,20 +11232,20 @@
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>maio 2025</t>
+          <t>março 2025</t>
         </is>
       </c>
       <c r="D293" t="n">
-        <v>274500</v>
+        <v>268300</v>
       </c>
       <c r="E293" t="n">
-        <v>274500</v>
+        <v>268300</v>
       </c>
       <c r="F293" t="n">
-        <v>2983900</v>
+        <v>2851300</v>
       </c>
       <c r="G293" t="n">
-        <v>10870</v>
+        <v>10627</v>
       </c>
       <c r="H293" t="inlineStr">
         <is>
@@ -11270,13 +11254,13 @@
       </c>
       <c r="I293" t="inlineStr">
         <is>
-          <t>2025-05</t>
+          <t>2025-03</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" s="1" t="n">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="B294" t="inlineStr">
         <is>
@@ -11285,20 +11269,20 @@
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>junho 2025</t>
+          <t>abril 2025</t>
         </is>
       </c>
       <c r="D294" t="n">
-        <v>277400</v>
+        <v>269300</v>
       </c>
       <c r="E294" t="n">
-        <v>277400</v>
+        <v>269300</v>
       </c>
       <c r="F294" t="n">
-        <v>3021700</v>
+        <v>2923200</v>
       </c>
       <c r="G294" t="n">
-        <v>10893</v>
+        <v>10855</v>
       </c>
       <c r="H294" t="inlineStr">
         <is>
@@ -11307,13 +11291,13 @@
       </c>
       <c r="I294" t="inlineStr">
         <is>
-          <t>2025-06</t>
+          <t>2025-04</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" s="1" t="n">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="B295" t="inlineStr">
         <is>
@@ -11322,20 +11306,20 @@
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>julho 2025</t>
+          <t>maio 2025</t>
         </is>
       </c>
       <c r="D295" t="n">
-        <v>280200</v>
+        <v>274500</v>
       </c>
       <c r="E295" t="n">
-        <v>280200</v>
+        <v>274500</v>
       </c>
       <c r="F295" t="n">
-        <v>3049600</v>
+        <v>2983900</v>
       </c>
       <c r="G295" t="n">
-        <v>10884</v>
+        <v>10870</v>
       </c>
       <c r="H295" t="inlineStr">
         <is>
@@ -11344,13 +11328,13 @@
       </c>
       <c r="I295" t="inlineStr">
         <is>
-          <t>2025-07</t>
+          <t>2025-05</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="A296" s="1" t="n">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="B296" t="inlineStr">
         <is>
@@ -11359,20 +11343,20 @@
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>agosto 2025</t>
+          <t>junho 2025</t>
         </is>
       </c>
       <c r="D296" t="n">
-        <v>281100</v>
+        <v>277400</v>
       </c>
       <c r="E296" t="n">
-        <v>281100</v>
+        <v>277400</v>
       </c>
       <c r="F296" t="n">
-        <v>3055800</v>
+        <v>3021700</v>
       </c>
       <c r="G296" t="n">
-        <v>10871</v>
+        <v>10893</v>
       </c>
       <c r="H296" t="inlineStr">
         <is>
@@ -11381,13 +11365,13 @@
       </c>
       <c r="I296" t="inlineStr">
         <is>
-          <t>2025-08</t>
+          <t>2025-06</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" s="1" t="n">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="B297" t="inlineStr">
         <is>
@@ -11396,20 +11380,20 @@
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>setembro 2025</t>
+          <t>julho 2025</t>
         </is>
       </c>
       <c r="D297" t="n">
-        <v>281300</v>
+        <v>280200</v>
       </c>
       <c r="E297" t="n">
-        <v>281300</v>
+        <v>280200</v>
       </c>
       <c r="F297" t="n">
-        <v>3059000</v>
+        <v>3049600</v>
       </c>
       <c r="G297" t="n">
-        <v>10875</v>
+        <v>10884</v>
       </c>
       <c r="H297" t="inlineStr">
         <is>
@@ -11418,13 +11402,13 @@
       </c>
       <c r="I297" t="inlineStr">
         <is>
-          <t>2025-09</t>
+          <t>2025-07</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" s="1" t="n">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="B298" t="inlineStr">
         <is>
@@ -11433,20 +11417,20 @@
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>outubro 2025</t>
+          <t>agosto 2025</t>
         </is>
       </c>
       <c r="D298" t="n">
-        <v>281300</v>
+        <v>281100</v>
       </c>
       <c r="E298" t="n">
-        <v>281300</v>
+        <v>281100</v>
       </c>
       <c r="F298" t="n">
-        <v>3055600</v>
+        <v>3055800</v>
       </c>
       <c r="G298" t="n">
-        <v>10862</v>
+        <v>10871</v>
       </c>
       <c r="H298" t="inlineStr">
         <is>
@@ -11455,13 +11439,13 @@
       </c>
       <c r="I298" t="inlineStr">
         <is>
-          <t>2025-10</t>
+          <t>2025-08</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" s="1" t="n">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="B299" t="inlineStr">
         <is>
@@ -11470,20 +11454,20 @@
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>novembro 2025</t>
+          <t>setembro 2025</t>
         </is>
       </c>
       <c r="D299" t="n">
-        <v>281000</v>
+        <v>281300</v>
       </c>
       <c r="E299" t="n">
-        <v>281000</v>
+        <v>281300</v>
       </c>
       <c r="F299" t="n">
-        <v>3052000</v>
+        <v>3059000</v>
       </c>
       <c r="G299" t="n">
-        <v>10861</v>
+        <v>10875</v>
       </c>
       <c r="H299" t="inlineStr">
         <is>
@@ -11492,13 +11476,13 @@
       </c>
       <c r="I299" t="inlineStr">
         <is>
-          <t>2025-11</t>
+          <t>2025-09</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="A300" s="1" t="n">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="B300" t="inlineStr">
         <is>
@@ -11507,17 +11491,17 @@
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>dezembro 2025</t>
+          <t>outubro 2025</t>
         </is>
       </c>
       <c r="D300" t="n">
-        <v>281000</v>
+        <v>281300</v>
       </c>
       <c r="E300" t="n">
-        <v>281000</v>
+        <v>281300</v>
       </c>
       <c r="F300" t="n">
-        <v>3052300</v>
+        <v>3055600</v>
       </c>
       <c r="G300" t="n">
         <v>10862</v>
@@ -11529,13 +11513,13 @@
       </c>
       <c r="I300" t="inlineStr">
         <is>
-          <t>2025-12</t>
+          <t>2025-10</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" s="1" t="n">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="B301" t="inlineStr">
         <is>
@@ -11544,20 +11528,20 @@
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>janeiro 2026</t>
+          <t>novembro 2025</t>
         </is>
       </c>
       <c r="D301" t="n">
-        <v>339300</v>
+        <v>281000</v>
       </c>
       <c r="E301" t="n">
-        <v>339300</v>
+        <v>281000</v>
       </c>
       <c r="F301" t="n">
-        <v>3469600</v>
+        <v>3052000</v>
       </c>
       <c r="G301" t="n">
-        <v>10226</v>
+        <v>10861</v>
       </c>
       <c r="H301" t="inlineStr">
         <is>
@@ -11566,13 +11550,13 @@
       </c>
       <c r="I301" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2025-11</t>
         </is>
       </c>
     </row>
     <row r="302">
       <c r="A302" s="1" t="n">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="B302" t="inlineStr">
         <is>
@@ -11581,20 +11565,20 @@
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>fevereiro 2026</t>
+          <t>dezembro 2025</t>
         </is>
       </c>
       <c r="D302" t="n">
-        <v>341000</v>
+        <v>281000</v>
       </c>
       <c r="E302" t="n">
-        <v>341000</v>
+        <v>281000</v>
       </c>
       <c r="F302" t="n">
-        <v>3599200</v>
+        <v>3052300</v>
       </c>
       <c r="G302" t="n">
-        <v>10555</v>
+        <v>10862</v>
       </c>
       <c r="H302" t="inlineStr">
         <is>
@@ -11603,13 +11587,13 @@
       </c>
       <c r="I302" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2025-12</t>
         </is>
       </c>
     </row>
     <row r="303">
       <c r="A303" s="1" t="n">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="B303" t="inlineStr">
         <is>
@@ -11618,20 +11602,20 @@
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>março 2026</t>
+          <t>janeiro 2026</t>
         </is>
       </c>
       <c r="D303" t="n">
-        <v>345200</v>
+        <v>339300</v>
       </c>
       <c r="E303" t="n">
-        <v>345200</v>
+        <v>339300</v>
       </c>
       <c r="F303" t="n">
-        <v>3823000</v>
+        <v>3469600</v>
       </c>
       <c r="G303" t="n">
-        <v>11075</v>
+        <v>10226</v>
       </c>
       <c r="H303" t="inlineStr">
         <is>
@@ -11640,46 +11624,141 @@
       </c>
       <c r="I303" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-01</t>
         </is>
       </c>
     </row>
     <row r="304">
       <c r="A304" s="1" t="n">
+        <v>149</v>
+      </c>
+      <c r="B304" t="inlineStr">
+        <is>
+          <t>Parana</t>
+        </is>
+      </c>
+      <c r="C304" t="inlineStr">
+        <is>
+          <t>fevereiro 2026</t>
+        </is>
+      </c>
+      <c r="D304" t="n">
+        <v>341000</v>
+      </c>
+      <c r="E304" t="n">
+        <v>341000</v>
+      </c>
+      <c r="F304" t="n">
+        <v>3599200</v>
+      </c>
+      <c r="G304" t="n">
+        <v>10555</v>
+      </c>
+      <c r="H304" t="inlineStr">
+        <is>
+          <t>milho</t>
+        </is>
+      </c>
+      <c r="I304" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" s="1" t="n">
+        <v>150</v>
+      </c>
+      <c r="B305" t="inlineStr">
+        <is>
+          <t>Parana</t>
+        </is>
+      </c>
+      <c r="C305" t="inlineStr">
+        <is>
+          <t>março 2026</t>
+        </is>
+      </c>
+      <c r="D305" t="n">
+        <v>345200</v>
+      </c>
+      <c r="E305" t="n">
+        <v>345200</v>
+      </c>
+      <c r="F305" t="n">
+        <v>3823000</v>
+      </c>
+      <c r="G305" t="n">
+        <v>11075</v>
+      </c>
+      <c r="H305" t="inlineStr">
+        <is>
+          <t>milho</t>
+        </is>
+      </c>
+      <c r="I305" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" s="1" t="n">
         <v>151</v>
       </c>
-      <c r="B304" t="inlineStr">
-        <is>
-          <t>Parana</t>
-        </is>
-      </c>
-      <c r="C304" t="inlineStr">
+      <c r="B306" t="inlineStr">
+        <is>
+          <t>Parana</t>
+        </is>
+      </c>
+      <c r="C306" t="inlineStr">
         <is>
           <t>abril 2026</t>
         </is>
       </c>
-      <c r="D304" t="n">
+      <c r="D306" t="n">
         <v>349700</v>
       </c>
-      <c r="E304" t="n">
+      <c r="E306" t="n">
         <v>349700</v>
       </c>
-      <c r="F304" t="n">
+      <c r="F306" t="n">
         <v>3939800</v>
       </c>
-      <c r="G304" t="n">
+      <c r="G306" t="n">
         <v>11266</v>
       </c>
-      <c r="H304" t="inlineStr">
-        <is>
-          <t>milho</t>
-        </is>
-      </c>
-      <c r="I304" t="inlineStr">
+      <c r="H306" t="inlineStr">
+        <is>
+          <t>milho</t>
+        </is>
+      </c>
+      <c r="I306" t="inlineStr">
         <is>
           <t>2026-04</t>
         </is>
       </c>
+    </row>
+    <row r="307">
+      <c r="A307" s="1" t="n">
+        <v>152</v>
+      </c>
+      <c r="B307" t="inlineStr">
+        <is>
+          <t>Fonte: IBGE - Levantamento Sistematico da Produçao Agrícola</t>
+        </is>
+      </c>
+      <c r="C307" t="inlineStr"/>
+      <c r="D307" t="inlineStr"/>
+      <c r="E307" t="inlineStr"/>
+      <c r="F307" t="inlineStr"/>
+      <c r="G307" t="inlineStr"/>
+      <c r="H307" t="inlineStr">
+        <is>
+          <t>milho</t>
+        </is>
+      </c>
+      <c r="I307" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
